--- a/diseases/d211/2020-2025.xlsx
+++ b/diseases/d211/2020-2025.xlsx
@@ -1015,7 +1015,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1257,7 +1257,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
@@ -1669,7 +1669,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
@@ -1911,7 +1911,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2323,7 +2323,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
@@ -2977,7 +2977,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
@@ -3219,7 +3219,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3631,7 +3631,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3873,7 +3873,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
@@ -4285,7 +4285,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
@@ -4527,7 +4527,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4939,7 +4939,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -5181,7 +5181,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
@@ -5593,7 +5593,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
@@ -5835,7 +5835,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -6247,7 +6247,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -6489,7 +6489,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
@@ -6901,7 +6901,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
@@ -7143,7 +7143,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -7555,7 +7555,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7797,7 +7797,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
@@ -8209,7 +8209,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
@@ -8451,7 +8451,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -8863,7 +8863,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -9105,7 +9105,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK40" t="inlineStr">
@@ -9517,7 +9517,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
@@ -9759,7 +9759,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -10171,7 +10171,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -10413,7 +10413,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
@@ -10825,7 +10825,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK48" t="inlineStr">
@@ -11067,7 +11067,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -11479,7 +11479,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -11721,7 +11721,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK52" t="inlineStr">
@@ -12133,7 +12133,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK54" t="inlineStr">
@@ -12375,7 +12375,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -12787,7 +12787,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -13029,7 +13029,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK58" t="inlineStr">
@@ -13441,7 +13441,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK60" t="inlineStr">
@@ -13683,7 +13683,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -14095,7 +14095,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -14337,7 +14337,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK64" t="inlineStr">
@@ -14749,7 +14749,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK66" t="inlineStr">
@@ -14991,7 +14991,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -15403,7 +15403,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -15645,7 +15645,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK70" t="inlineStr">
@@ -16057,7 +16057,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK72" t="inlineStr">
@@ -16299,7 +16299,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -16711,7 +16711,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -16953,7 +16953,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK76" t="inlineStr">
@@ -17365,7 +17365,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK78" t="inlineStr">
@@ -17607,7 +17607,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -18019,7 +18019,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -18261,7 +18261,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK82" t="inlineStr">
@@ -18673,7 +18673,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK84" t="inlineStr">
@@ -18915,7 +18915,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -19327,7 +19327,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -19569,7 +19569,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK88" t="inlineStr">
@@ -19981,7 +19981,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK90" t="inlineStr">
@@ -20223,7 +20223,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -20635,7 +20635,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -20877,7 +20877,7 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK94" t="inlineStr">
@@ -21289,7 +21289,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK96" t="inlineStr">
@@ -21531,7 +21531,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
@@ -21943,7 +21943,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -22185,7 +22185,7 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK100" t="inlineStr">
@@ -22597,7 +22597,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK102" t="inlineStr">
@@ -22839,7 +22839,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -23251,7 +23251,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
@@ -23493,7 +23493,7 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK106" t="inlineStr">
@@ -23905,7 +23905,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK108" t="inlineStr">
@@ -24147,7 +24147,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
@@ -24559,7 +24559,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -24801,7 +24801,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK112" t="inlineStr">
@@ -25213,7 +25213,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK114" t="inlineStr">
@@ -25455,7 +25455,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
@@ -25867,7 +25867,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK117" t="inlineStr">
@@ -26109,7 +26109,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK118" t="inlineStr">
@@ -26521,7 +26521,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK120" t="inlineStr">
@@ -26763,7 +26763,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK121" t="inlineStr">
@@ -27175,7 +27175,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
@@ -27417,7 +27417,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK124" t="inlineStr">
@@ -27829,7 +27829,7 @@
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK126" t="inlineStr">
@@ -28071,7 +28071,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK127" t="inlineStr">
@@ -28483,7 +28483,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK129" t="inlineStr">
@@ -28725,7 +28725,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK130" t="inlineStr">
@@ -29137,7 +29137,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK132" t="inlineStr">
@@ -29379,7 +29379,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK133" t="inlineStr">
@@ -29791,7 +29791,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
@@ -30033,7 +30033,7 @@
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK136" t="inlineStr">
@@ -30445,7 +30445,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK138" t="inlineStr">
@@ -30687,7 +30687,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK139" t="inlineStr">
@@ -31099,7 +31099,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK141" t="inlineStr">
@@ -31341,7 +31341,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK142" t="inlineStr">
@@ -31753,7 +31753,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK144" t="inlineStr">
@@ -31995,7 +31995,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK145" t="inlineStr">
@@ -32407,7 +32407,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">
@@ -32649,7 +32649,7 @@
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK148" t="inlineStr">
@@ -33061,7 +33061,7 @@
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK150" t="inlineStr">
@@ -33303,7 +33303,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK151" t="inlineStr">
@@ -33715,7 +33715,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK153" t="inlineStr">
@@ -33957,7 +33957,7 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK154" t="inlineStr">
@@ -34369,7 +34369,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK156" t="inlineStr">
@@ -34611,7 +34611,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK157" t="inlineStr">
@@ -35023,7 +35023,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK159" t="inlineStr">
@@ -35265,7 +35265,7 @@
       </c>
       <c r="AJ160" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK160" t="inlineStr">
@@ -35677,7 +35677,7 @@
       </c>
       <c r="AJ162" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK162" t="inlineStr">
@@ -35919,7 +35919,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK163" t="inlineStr">
@@ -36331,7 +36331,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK165" t="inlineStr">
@@ -36573,7 +36573,7 @@
       </c>
       <c r="AJ166" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK166" t="inlineStr">
@@ -36985,7 +36985,7 @@
       </c>
       <c r="AJ168" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK168" t="inlineStr">
@@ -37227,7 +37227,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK169" t="inlineStr">
@@ -37639,7 +37639,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK171" t="inlineStr">
@@ -37881,7 +37881,7 @@
       </c>
       <c r="AJ172" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK172" t="inlineStr">
@@ -38293,7 +38293,7 @@
       </c>
       <c r="AJ174" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK174" t="inlineStr">
@@ -38535,7 +38535,7 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK175" t="inlineStr">
@@ -38947,7 +38947,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK177" t="inlineStr">
@@ -39189,7 +39189,7 @@
       </c>
       <c r="AJ178" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK178" t="inlineStr">
@@ -39601,7 +39601,7 @@
       </c>
       <c r="AJ180" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK180" t="inlineStr">
@@ -39843,7 +39843,7 @@
       </c>
       <c r="AJ181" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK181" t="inlineStr">
@@ -40255,7 +40255,7 @@
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK183" t="inlineStr">
@@ -40497,7 +40497,7 @@
       </c>
       <c r="AJ184" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK184" t="inlineStr">
@@ -40909,7 +40909,7 @@
       </c>
       <c r="AJ186" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK186" t="inlineStr">
@@ -41151,7 +41151,7 @@
       </c>
       <c r="AJ187" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK187" t="inlineStr">
@@ -41563,7 +41563,7 @@
       </c>
       <c r="AJ189" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK189" t="inlineStr">
@@ -41805,7 +41805,7 @@
       </c>
       <c r="AJ190" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK190" t="inlineStr">
@@ -42217,7 +42217,7 @@
       </c>
       <c r="AJ192" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK192" t="inlineStr">
@@ -42459,7 +42459,7 @@
       </c>
       <c r="AJ193" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK193" t="inlineStr">
@@ -42871,7 +42871,7 @@
       </c>
       <c r="AJ195" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK195" t="inlineStr">
@@ -43113,7 +43113,7 @@
       </c>
       <c r="AJ196" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK196" t="inlineStr">
@@ -43525,7 +43525,7 @@
       </c>
       <c r="AJ198" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK198" t="inlineStr">
@@ -43767,7 +43767,7 @@
       </c>
       <c r="AJ199" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK199" t="inlineStr">
@@ -44179,7 +44179,7 @@
       </c>
       <c r="AJ201" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK201" t="inlineStr">
@@ -44421,7 +44421,7 @@
       </c>
       <c r="AJ202" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK202" t="inlineStr">
@@ -44833,7 +44833,7 @@
       </c>
       <c r="AJ204" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK204" t="inlineStr">
@@ -45075,7 +45075,7 @@
       </c>
       <c r="AJ205" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK205" t="inlineStr">
@@ -45487,7 +45487,7 @@
       </c>
       <c r="AJ207" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK207" t="inlineStr">
@@ -45729,7 +45729,7 @@
       </c>
       <c r="AJ208" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK208" t="inlineStr">
@@ -46141,7 +46141,7 @@
       </c>
       <c r="AJ210" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK210" t="inlineStr">
@@ -46383,7 +46383,7 @@
       </c>
       <c r="AJ211" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK211" t="inlineStr">
@@ -46795,7 +46795,7 @@
       </c>
       <c r="AJ213" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK213" t="inlineStr">
@@ -47037,7 +47037,7 @@
       </c>
       <c r="AJ214" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK214" t="inlineStr">
@@ -47449,7 +47449,7 @@
       </c>
       <c r="AJ216" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK216" t="inlineStr">
@@ -47691,7 +47691,7 @@
       </c>
       <c r="AJ217" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK217" t="inlineStr">
@@ -48103,7 +48103,7 @@
       </c>
       <c r="AJ219" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK219" t="inlineStr">
@@ -48345,7 +48345,7 @@
       </c>
       <c r="AJ220" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK220" t="inlineStr">
@@ -48757,7 +48757,7 @@
       </c>
       <c r="AJ222" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK222" t="inlineStr">
@@ -48999,7 +48999,7 @@
       </c>
       <c r="AJ223" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK223" t="inlineStr">
@@ -49411,7 +49411,7 @@
       </c>
       <c r="AJ225" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK225" t="inlineStr">
@@ -49653,7 +49653,7 @@
       </c>
       <c r="AJ226" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK226" t="inlineStr">
@@ -50065,7 +50065,7 @@
       </c>
       <c r="AJ228" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK228" t="inlineStr">
@@ -50307,7 +50307,7 @@
       </c>
       <c r="AJ229" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK229" t="inlineStr">
@@ -50719,7 +50719,7 @@
       </c>
       <c r="AJ231" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK231" t="inlineStr">
@@ -50961,7 +50961,7 @@
       </c>
       <c r="AJ232" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK232" t="inlineStr">
@@ -51373,7 +51373,7 @@
       </c>
       <c r="AJ234" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK234" t="inlineStr">
@@ -51615,7 +51615,7 @@
       </c>
       <c r="AJ235" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK235" t="inlineStr">
@@ -52027,7 +52027,7 @@
       </c>
       <c r="AJ237" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK237" t="inlineStr">
@@ -52269,7 +52269,7 @@
       </c>
       <c r="AJ238" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK238" t="inlineStr">
@@ -52681,7 +52681,7 @@
       </c>
       <c r="AJ240" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK240" t="inlineStr">
@@ -52923,7 +52923,7 @@
       </c>
       <c r="AJ241" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK241" t="inlineStr">
@@ -53335,7 +53335,7 @@
       </c>
       <c r="AJ243" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK243" t="inlineStr">
@@ -53577,7 +53577,7 @@
       </c>
       <c r="AJ244" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK244" t="inlineStr">
@@ -53989,7 +53989,7 @@
       </c>
       <c r="AJ246" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK246" t="inlineStr">
@@ -54231,7 +54231,7 @@
       </c>
       <c r="AJ247" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK247" t="inlineStr">
@@ -54643,7 +54643,7 @@
       </c>
       <c r="AJ249" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK249" t="inlineStr">
@@ -54885,7 +54885,7 @@
       </c>
       <c r="AJ250" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK250" t="inlineStr">
@@ -55297,7 +55297,7 @@
       </c>
       <c r="AJ252" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK252" t="inlineStr">
@@ -55539,7 +55539,7 @@
       </c>
       <c r="AJ253" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK253" t="inlineStr">
@@ -55951,7 +55951,7 @@
       </c>
       <c r="AJ255" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK255" t="inlineStr">
@@ -56193,7 +56193,7 @@
       </c>
       <c r="AJ256" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK256" t="inlineStr">
@@ -56605,7 +56605,7 @@
       </c>
       <c r="AJ258" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK258" t="inlineStr">
@@ -56847,7 +56847,7 @@
       </c>
       <c r="AJ259" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK259" t="inlineStr">
@@ -57259,7 +57259,7 @@
       </c>
       <c r="AJ261" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK261" t="inlineStr">
@@ -57501,7 +57501,7 @@
       </c>
       <c r="AJ262" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK262" t="inlineStr">
@@ -57913,7 +57913,7 @@
       </c>
       <c r="AJ264" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK264" t="inlineStr">
@@ -58155,7 +58155,7 @@
       </c>
       <c r="AJ265" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK265" t="inlineStr">
@@ -58567,7 +58567,7 @@
       </c>
       <c r="AJ267" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK267" t="inlineStr">
@@ -58809,7 +58809,7 @@
       </c>
       <c r="AJ268" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK268" t="inlineStr">
@@ -59221,7 +59221,7 @@
       </c>
       <c r="AJ270" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK270" t="inlineStr">
@@ -59463,7 +59463,7 @@
       </c>
       <c r="AJ271" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK271" t="inlineStr">
@@ -59875,7 +59875,7 @@
       </c>
       <c r="AJ273" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK273" t="inlineStr">
@@ -60117,7 +60117,7 @@
       </c>
       <c r="AJ274" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK274" t="inlineStr">
@@ -60529,7 +60529,7 @@
       </c>
       <c r="AJ276" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK276" t="inlineStr">
@@ -60771,7 +60771,7 @@
       </c>
       <c r="AJ277" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK277" t="inlineStr">
@@ -61183,7 +61183,7 @@
       </c>
       <c r="AJ279" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK279" t="inlineStr">
@@ -61425,7 +61425,7 @@
       </c>
       <c r="AJ280" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK280" t="inlineStr">
@@ -61837,7 +61837,7 @@
       </c>
       <c r="AJ282" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK282" t="inlineStr">
@@ -62079,7 +62079,7 @@
       </c>
       <c r="AJ283" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK283" t="inlineStr">
@@ -62491,7 +62491,7 @@
       </c>
       <c r="AJ285" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK285" t="inlineStr">
@@ -62733,7 +62733,7 @@
       </c>
       <c r="AJ286" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK286" t="inlineStr">
@@ -63145,7 +63145,7 @@
       </c>
       <c r="AJ288" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK288" t="inlineStr">
@@ -63387,7 +63387,7 @@
       </c>
       <c r="AJ289" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK289" t="inlineStr">
@@ -63799,7 +63799,7 @@
       </c>
       <c r="AJ291" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK291" t="inlineStr">
@@ -64041,7 +64041,7 @@
       </c>
       <c r="AJ292" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK292" t="inlineStr">
@@ -64453,7 +64453,7 @@
       </c>
       <c r="AJ294" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK294" t="inlineStr">
@@ -64695,7 +64695,7 @@
       </c>
       <c r="AJ295" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK295" t="inlineStr">
@@ -65107,7 +65107,7 @@
       </c>
       <c r="AJ297" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK297" t="inlineStr">
@@ -65349,7 +65349,7 @@
       </c>
       <c r="AJ298" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK298" t="inlineStr">
@@ -65761,7 +65761,7 @@
       </c>
       <c r="AJ300" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK300" t="inlineStr">
@@ -66003,7 +66003,7 @@
       </c>
       <c r="AJ301" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK301" t="inlineStr">
@@ -66415,7 +66415,7 @@
       </c>
       <c r="AJ303" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK303" t="inlineStr">
@@ -66657,7 +66657,7 @@
       </c>
       <c r="AJ304" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK304" t="inlineStr">
@@ -67069,7 +67069,7 @@
       </c>
       <c r="AJ306" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK306" t="inlineStr">
@@ -67311,7 +67311,7 @@
       </c>
       <c r="AJ307" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK307" t="inlineStr">
@@ -67723,7 +67723,7 @@
       </c>
       <c r="AJ309" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK309" t="inlineStr">
@@ -67965,7 +67965,7 @@
       </c>
       <c r="AJ310" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK310" t="inlineStr">
@@ -68377,7 +68377,7 @@
       </c>
       <c r="AJ312" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK312" t="inlineStr">
@@ -68619,7 +68619,7 @@
       </c>
       <c r="AJ313" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK313" t="inlineStr">

--- a/diseases/d211/2020-2025.xlsx
+++ b/diseases/d211/2020-2025.xlsx
@@ -1015,7 +1015,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1257,7 +1257,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
@@ -1669,7 +1669,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
@@ -1911,7 +1911,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2323,7 +2323,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
@@ -2977,7 +2977,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
@@ -3219,7 +3219,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3631,7 +3631,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3873,7 +3873,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
@@ -4285,7 +4285,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
@@ -4527,7 +4527,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4939,7 +4939,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -5181,7 +5181,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
@@ -5593,7 +5593,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
@@ -5835,7 +5835,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -6247,7 +6247,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -6489,7 +6489,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
@@ -6901,7 +6901,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
@@ -7143,7 +7143,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -7555,7 +7555,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7797,7 +7797,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
@@ -8209,7 +8209,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
@@ -8451,7 +8451,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -8863,7 +8863,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -9105,7 +9105,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK40" t="inlineStr">
@@ -9517,7 +9517,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
@@ -9759,7 +9759,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -10171,7 +10171,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -10413,7 +10413,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
@@ -10825,7 +10825,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK48" t="inlineStr">
@@ -11067,7 +11067,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -11479,7 +11479,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -11721,7 +11721,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK52" t="inlineStr">
@@ -12133,7 +12133,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK54" t="inlineStr">
@@ -12375,7 +12375,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -12787,7 +12787,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -13029,7 +13029,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK58" t="inlineStr">
@@ -13441,7 +13441,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK60" t="inlineStr">
@@ -13683,7 +13683,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -14095,7 +14095,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -14337,7 +14337,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK64" t="inlineStr">
@@ -14749,7 +14749,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK66" t="inlineStr">
@@ -14991,7 +14991,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -15403,7 +15403,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -15645,7 +15645,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK70" t="inlineStr">
@@ -16057,7 +16057,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK72" t="inlineStr">
@@ -16299,7 +16299,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -16711,7 +16711,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -16953,7 +16953,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK76" t="inlineStr">
@@ -17365,7 +17365,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK78" t="inlineStr">
@@ -17607,7 +17607,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -18019,7 +18019,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -18261,7 +18261,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK82" t="inlineStr">
@@ -18673,7 +18673,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK84" t="inlineStr">
@@ -18915,7 +18915,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -19327,7 +19327,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -19569,7 +19569,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK88" t="inlineStr">
@@ -19981,7 +19981,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK90" t="inlineStr">
@@ -20223,7 +20223,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -20635,7 +20635,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -20877,7 +20877,7 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK94" t="inlineStr">
@@ -21289,7 +21289,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK96" t="inlineStr">
@@ -21531,7 +21531,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
@@ -21943,7 +21943,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -22185,7 +22185,7 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK100" t="inlineStr">
@@ -22597,7 +22597,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK102" t="inlineStr">
@@ -22839,7 +22839,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -23251,7 +23251,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
@@ -23493,7 +23493,7 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK106" t="inlineStr">
@@ -23905,7 +23905,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK108" t="inlineStr">
@@ -24147,7 +24147,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
@@ -24559,7 +24559,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -24801,7 +24801,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK112" t="inlineStr">
@@ -25213,7 +25213,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK114" t="inlineStr">
@@ -25455,7 +25455,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
@@ -25867,7 +25867,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK117" t="inlineStr">
@@ -26109,7 +26109,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK118" t="inlineStr">
@@ -26521,7 +26521,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK120" t="inlineStr">
@@ -26763,7 +26763,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK121" t="inlineStr">
@@ -27175,7 +27175,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
@@ -27417,7 +27417,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK124" t="inlineStr">
@@ -27829,7 +27829,7 @@
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK126" t="inlineStr">
@@ -28071,7 +28071,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK127" t="inlineStr">
@@ -28483,7 +28483,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK129" t="inlineStr">
@@ -28725,7 +28725,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK130" t="inlineStr">
@@ -29137,7 +29137,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK132" t="inlineStr">
@@ -29379,7 +29379,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK133" t="inlineStr">
@@ -29791,7 +29791,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
@@ -30033,7 +30033,7 @@
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK136" t="inlineStr">
@@ -30445,7 +30445,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK138" t="inlineStr">
@@ -30687,7 +30687,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK139" t="inlineStr">
@@ -31099,7 +31099,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK141" t="inlineStr">
@@ -31341,7 +31341,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK142" t="inlineStr">
@@ -31753,7 +31753,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK144" t="inlineStr">
@@ -31995,7 +31995,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK145" t="inlineStr">
@@ -32407,7 +32407,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">
@@ -32649,7 +32649,7 @@
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK148" t="inlineStr">
@@ -33061,7 +33061,7 @@
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK150" t="inlineStr">
@@ -33303,7 +33303,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK151" t="inlineStr">
@@ -33715,7 +33715,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK153" t="inlineStr">
@@ -33957,7 +33957,7 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK154" t="inlineStr">
@@ -34369,7 +34369,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK156" t="inlineStr">
@@ -34611,7 +34611,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK157" t="inlineStr">
@@ -35023,7 +35023,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK159" t="inlineStr">
@@ -35265,7 +35265,7 @@
       </c>
       <c r="AJ160" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK160" t="inlineStr">
@@ -35677,7 +35677,7 @@
       </c>
       <c r="AJ162" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK162" t="inlineStr">
@@ -35919,7 +35919,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK163" t="inlineStr">
@@ -36331,7 +36331,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK165" t="inlineStr">
@@ -36573,7 +36573,7 @@
       </c>
       <c r="AJ166" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK166" t="inlineStr">
@@ -36985,7 +36985,7 @@
       </c>
       <c r="AJ168" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK168" t="inlineStr">
@@ -37227,7 +37227,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK169" t="inlineStr">
@@ -37639,7 +37639,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK171" t="inlineStr">
@@ -37881,7 +37881,7 @@
       </c>
       <c r="AJ172" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK172" t="inlineStr">
@@ -38293,7 +38293,7 @@
       </c>
       <c r="AJ174" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK174" t="inlineStr">
@@ -38535,7 +38535,7 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK175" t="inlineStr">
@@ -38947,7 +38947,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK177" t="inlineStr">
@@ -39189,7 +39189,7 @@
       </c>
       <c r="AJ178" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK178" t="inlineStr">
@@ -39601,7 +39601,7 @@
       </c>
       <c r="AJ180" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK180" t="inlineStr">
@@ -39843,7 +39843,7 @@
       </c>
       <c r="AJ181" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK181" t="inlineStr">
@@ -40255,7 +40255,7 @@
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK183" t="inlineStr">
@@ -40497,7 +40497,7 @@
       </c>
       <c r="AJ184" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK184" t="inlineStr">
@@ -40909,7 +40909,7 @@
       </c>
       <c r="AJ186" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK186" t="inlineStr">
@@ -41151,7 +41151,7 @@
       </c>
       <c r="AJ187" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK187" t="inlineStr">
@@ -41563,7 +41563,7 @@
       </c>
       <c r="AJ189" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK189" t="inlineStr">
@@ -41805,7 +41805,7 @@
       </c>
       <c r="AJ190" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK190" t="inlineStr">
@@ -42217,7 +42217,7 @@
       </c>
       <c r="AJ192" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK192" t="inlineStr">
@@ -42459,7 +42459,7 @@
       </c>
       <c r="AJ193" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK193" t="inlineStr">
@@ -42871,7 +42871,7 @@
       </c>
       <c r="AJ195" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK195" t="inlineStr">
@@ -43113,7 +43113,7 @@
       </c>
       <c r="AJ196" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK196" t="inlineStr">
@@ -43525,7 +43525,7 @@
       </c>
       <c r="AJ198" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK198" t="inlineStr">
@@ -43767,7 +43767,7 @@
       </c>
       <c r="AJ199" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK199" t="inlineStr">
@@ -44179,7 +44179,7 @@
       </c>
       <c r="AJ201" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK201" t="inlineStr">
@@ -44421,7 +44421,7 @@
       </c>
       <c r="AJ202" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK202" t="inlineStr">
@@ -44833,7 +44833,7 @@
       </c>
       <c r="AJ204" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK204" t="inlineStr">
@@ -45075,7 +45075,7 @@
       </c>
       <c r="AJ205" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK205" t="inlineStr">
@@ -45487,7 +45487,7 @@
       </c>
       <c r="AJ207" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK207" t="inlineStr">
@@ -45729,7 +45729,7 @@
       </c>
       <c r="AJ208" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK208" t="inlineStr">
@@ -46141,7 +46141,7 @@
       </c>
       <c r="AJ210" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK210" t="inlineStr">
@@ -46383,7 +46383,7 @@
       </c>
       <c r="AJ211" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK211" t="inlineStr">
@@ -46795,7 +46795,7 @@
       </c>
       <c r="AJ213" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK213" t="inlineStr">
@@ -47037,7 +47037,7 @@
       </c>
       <c r="AJ214" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK214" t="inlineStr">
@@ -47449,7 +47449,7 @@
       </c>
       <c r="AJ216" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK216" t="inlineStr">
@@ -47691,7 +47691,7 @@
       </c>
       <c r="AJ217" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK217" t="inlineStr">
@@ -48103,7 +48103,7 @@
       </c>
       <c r="AJ219" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK219" t="inlineStr">
@@ -48345,7 +48345,7 @@
       </c>
       <c r="AJ220" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK220" t="inlineStr">
@@ -48757,7 +48757,7 @@
       </c>
       <c r="AJ222" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK222" t="inlineStr">
@@ -48999,7 +48999,7 @@
       </c>
       <c r="AJ223" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK223" t="inlineStr">
@@ -49411,7 +49411,7 @@
       </c>
       <c r="AJ225" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK225" t="inlineStr">
@@ -49653,7 +49653,7 @@
       </c>
       <c r="AJ226" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK226" t="inlineStr">
@@ -50065,7 +50065,7 @@
       </c>
       <c r="AJ228" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK228" t="inlineStr">
@@ -50307,7 +50307,7 @@
       </c>
       <c r="AJ229" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK229" t="inlineStr">
@@ -50719,7 +50719,7 @@
       </c>
       <c r="AJ231" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK231" t="inlineStr">
@@ -50961,7 +50961,7 @@
       </c>
       <c r="AJ232" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK232" t="inlineStr">
@@ -51373,7 +51373,7 @@
       </c>
       <c r="AJ234" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK234" t="inlineStr">
@@ -51615,7 +51615,7 @@
       </c>
       <c r="AJ235" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK235" t="inlineStr">
@@ -52027,7 +52027,7 @@
       </c>
       <c r="AJ237" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK237" t="inlineStr">
@@ -52269,7 +52269,7 @@
       </c>
       <c r="AJ238" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK238" t="inlineStr">
@@ -52681,7 +52681,7 @@
       </c>
       <c r="AJ240" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK240" t="inlineStr">
@@ -52923,7 +52923,7 @@
       </c>
       <c r="AJ241" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK241" t="inlineStr">
@@ -53335,7 +53335,7 @@
       </c>
       <c r="AJ243" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK243" t="inlineStr">
@@ -53577,7 +53577,7 @@
       </c>
       <c r="AJ244" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK244" t="inlineStr">
@@ -53989,7 +53989,7 @@
       </c>
       <c r="AJ246" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK246" t="inlineStr">
@@ -54231,7 +54231,7 @@
       </c>
       <c r="AJ247" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK247" t="inlineStr">
@@ -54643,7 +54643,7 @@
       </c>
       <c r="AJ249" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK249" t="inlineStr">
@@ -54885,7 +54885,7 @@
       </c>
       <c r="AJ250" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK250" t="inlineStr">
@@ -55297,7 +55297,7 @@
       </c>
       <c r="AJ252" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK252" t="inlineStr">
@@ -55539,7 +55539,7 @@
       </c>
       <c r="AJ253" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK253" t="inlineStr">
@@ -55951,7 +55951,7 @@
       </c>
       <c r="AJ255" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK255" t="inlineStr">
@@ -56193,7 +56193,7 @@
       </c>
       <c r="AJ256" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK256" t="inlineStr">
@@ -56605,7 +56605,7 @@
       </c>
       <c r="AJ258" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK258" t="inlineStr">
@@ -56847,7 +56847,7 @@
       </c>
       <c r="AJ259" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK259" t="inlineStr">
@@ -57259,7 +57259,7 @@
       </c>
       <c r="AJ261" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK261" t="inlineStr">
@@ -57501,7 +57501,7 @@
       </c>
       <c r="AJ262" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK262" t="inlineStr">
@@ -57913,7 +57913,7 @@
       </c>
       <c r="AJ264" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK264" t="inlineStr">
@@ -58155,7 +58155,7 @@
       </c>
       <c r="AJ265" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK265" t="inlineStr">
@@ -58567,7 +58567,7 @@
       </c>
       <c r="AJ267" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK267" t="inlineStr">
@@ -58809,7 +58809,7 @@
       </c>
       <c r="AJ268" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK268" t="inlineStr">
@@ -59221,7 +59221,7 @@
       </c>
       <c r="AJ270" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK270" t="inlineStr">
@@ -59463,7 +59463,7 @@
       </c>
       <c r="AJ271" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK271" t="inlineStr">
@@ -59875,7 +59875,7 @@
       </c>
       <c r="AJ273" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK273" t="inlineStr">
@@ -60117,7 +60117,7 @@
       </c>
       <c r="AJ274" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK274" t="inlineStr">
@@ -60529,7 +60529,7 @@
       </c>
       <c r="AJ276" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK276" t="inlineStr">
@@ -60771,7 +60771,7 @@
       </c>
       <c r="AJ277" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK277" t="inlineStr">
@@ -61183,7 +61183,7 @@
       </c>
       <c r="AJ279" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK279" t="inlineStr">
@@ -61425,7 +61425,7 @@
       </c>
       <c r="AJ280" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK280" t="inlineStr">
@@ -61837,7 +61837,7 @@
       </c>
       <c r="AJ282" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK282" t="inlineStr">
@@ -62079,7 +62079,7 @@
       </c>
       <c r="AJ283" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK283" t="inlineStr">
@@ -62491,7 +62491,7 @@
       </c>
       <c r="AJ285" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK285" t="inlineStr">
@@ -62733,7 +62733,7 @@
       </c>
       <c r="AJ286" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK286" t="inlineStr">
@@ -63145,7 +63145,7 @@
       </c>
       <c r="AJ288" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK288" t="inlineStr">
@@ -63387,7 +63387,7 @@
       </c>
       <c r="AJ289" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK289" t="inlineStr">
@@ -63799,7 +63799,7 @@
       </c>
       <c r="AJ291" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK291" t="inlineStr">
@@ -64041,7 +64041,7 @@
       </c>
       <c r="AJ292" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK292" t="inlineStr">
@@ -64453,7 +64453,7 @@
       </c>
       <c r="AJ294" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK294" t="inlineStr">
@@ -64695,7 +64695,7 @@
       </c>
       <c r="AJ295" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK295" t="inlineStr">
@@ -65107,7 +65107,7 @@
       </c>
       <c r="AJ297" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK297" t="inlineStr">
@@ -65349,7 +65349,7 @@
       </c>
       <c r="AJ298" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK298" t="inlineStr">
@@ -65761,7 +65761,7 @@
       </c>
       <c r="AJ300" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK300" t="inlineStr">
@@ -66003,7 +66003,7 @@
       </c>
       <c r="AJ301" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK301" t="inlineStr">
@@ -66415,7 +66415,7 @@
       </c>
       <c r="AJ303" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK303" t="inlineStr">
@@ -66657,7 +66657,7 @@
       </c>
       <c r="AJ304" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK304" t="inlineStr">
@@ -67069,7 +67069,7 @@
       </c>
       <c r="AJ306" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK306" t="inlineStr">
@@ -67311,7 +67311,7 @@
       </c>
       <c r="AJ307" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK307" t="inlineStr">
@@ -67723,7 +67723,7 @@
       </c>
       <c r="AJ309" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK309" t="inlineStr">
@@ -67965,7 +67965,7 @@
       </c>
       <c r="AJ310" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK310" t="inlineStr">
@@ -68377,7 +68377,7 @@
       </c>
       <c r="AJ312" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK312" t="inlineStr">
@@ -68619,7 +68619,7 @@
       </c>
       <c r="AJ313" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK313" t="inlineStr">

--- a/diseases/d211/2020-2025.xlsx
+++ b/diseases/d211/2020-2025.xlsx
@@ -768,9 +768,6 @@
       <c r="P2" t="n">
         <v>575</v>
       </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
       <c r="R2" t="n">
         <v>0.1664608482015126</v>
       </c>
@@ -1422,9 +1419,6 @@
       <c r="P5" t="n">
         <v>509</v>
       </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
       <c r="R5" t="n">
         <v>0.147354037799252</v>
       </c>
@@ -2076,9 +2070,6 @@
       <c r="P8" t="n">
         <v>587</v>
       </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
       <c r="R8" t="n">
         <v>0.1699348137291963</v>
       </c>
@@ -2730,9 +2721,6 @@
       <c r="P11" t="n">
         <v>798</v>
       </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
       <c r="R11" t="n">
         <v>0.2310187075909687</v>
       </c>
@@ -3384,9 +3372,6 @@
       <c r="P14" t="n">
         <v>712</v>
       </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
       <c r="R14" t="n">
         <v>0.2061219546425686</v>
       </c>
@@ -4038,9 +4023,6 @@
       <c r="P17" t="n">
         <v>872</v>
       </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
       <c r="R17" t="n">
         <v>0.2524414950116851</v>
       </c>
@@ -4692,9 +4674,6 @@
       <c r="P20" t="n">
         <v>967</v>
       </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
       <c r="R20" t="n">
         <v>0.2799437221058481</v>
       </c>
@@ -5346,9 +5325,6 @@
       <c r="P23" t="n">
         <v>964</v>
       </c>
-      <c r="Q23" t="n">
-        <v>0</v>
-      </c>
       <c r="R23" t="n">
         <v>0.2790752307239271</v>
       </c>
@@ -6000,9 +5976,6 @@
       <c r="P26" t="n">
         <v>897</v>
       </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
       <c r="R26" t="n">
         <v>0.2596789231943596</v>
       </c>
@@ -6654,9 +6627,6 @@
       <c r="P29" t="n">
         <v>871</v>
       </c>
-      <c r="Q29" t="n">
-        <v>0</v>
-      </c>
       <c r="R29" t="n">
         <v>0.2521519978843781</v>
       </c>
@@ -7308,9 +7278,6 @@
       <c r="P32" t="n">
         <v>868</v>
       </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
       <c r="R32" t="n">
         <v>0.2512835065024572</v>
       </c>
@@ -7962,9 +7929,6 @@
       <c r="P35" t="n">
         <v>966</v>
       </c>
-      <c r="Q35" t="n">
-        <v>0</v>
-      </c>
       <c r="R35" t="n">
         <v>0.2796542249785411</v>
       </c>
@@ -8616,9 +8580,6 @@
       <c r="P38" t="n">
         <v>781</v>
       </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
       <c r="R38" t="n">
         <v>0.2260972564267501</v>
       </c>
@@ -9270,9 +9231,6 @@
       <c r="P41" t="n">
         <v>770</v>
       </c>
-      <c r="Q41" t="n">
-        <v>0</v>
-      </c>
       <c r="R41" t="n">
         <v>0.2229127880263733</v>
       </c>
@@ -9924,9 +9882,6 @@
       <c r="P44" t="n">
         <v>805</v>
       </c>
-      <c r="Q44" t="n">
-        <v>0</v>
-      </c>
       <c r="R44" t="n">
         <v>0.2330451874821176</v>
       </c>
@@ -10578,9 +10533,6 @@
       <c r="P47" t="n">
         <v>854</v>
       </c>
-      <c r="Q47" t="n">
-        <v>0</v>
-      </c>
       <c r="R47" t="n">
         <v>0.2472305467201595</v>
       </c>
@@ -11232,9 +11184,6 @@
       <c r="P50" t="n">
         <v>657</v>
       </c>
-      <c r="Q50" t="n">
-        <v>0</v>
-      </c>
       <c r="R50" t="n">
         <v>0.1901996126406848</v>
       </c>
@@ -11886,9 +11835,6 @@
       <c r="P53" t="n">
         <v>974</v>
       </c>
-      <c r="Q53" t="n">
-        <v>0</v>
-      </c>
       <c r="R53" t="n">
         <v>0.2819702019969969</v>
       </c>
@@ -12540,9 +12486,6 @@
       <c r="P56" t="n">
         <v>804</v>
       </c>
-      <c r="Q56" t="n">
-        <v>0</v>
-      </c>
       <c r="R56" t="n">
         <v>0.2327556903548106</v>
       </c>
@@ -13194,9 +13137,6 @@
       <c r="P59" t="n">
         <v>794</v>
       </c>
-      <c r="Q59" t="n">
-        <v>0</v>
-      </c>
       <c r="R59" t="n">
         <v>0.2298607190817408</v>
       </c>
@@ -13848,9 +13788,6 @@
       <c r="P62" t="n">
         <v>652</v>
       </c>
-      <c r="Q62" t="n">
-        <v>0</v>
-      </c>
       <c r="R62" t="n">
         <v>0.1887521270041499</v>
       </c>
@@ -14502,9 +14439,6 @@
       <c r="P65" t="n">
         <v>567</v>
       </c>
-      <c r="Q65" t="n">
-        <v>0</v>
-      </c>
       <c r="R65" t="n">
         <v>0.1641448711830567</v>
       </c>
@@ -15156,9 +15090,6 @@
       <c r="P68" t="n">
         <v>662</v>
       </c>
-      <c r="Q68" t="n">
-        <v>0</v>
-      </c>
       <c r="R68" t="n">
         <v>0.1916470982772197</v>
       </c>
@@ -15810,9 +15741,6 @@
       <c r="P71" t="n">
         <v>752</v>
       </c>
-      <c r="Q71" t="n">
-        <v>0</v>
-      </c>
       <c r="R71" t="n">
         <v>0.2177018397348477</v>
       </c>
@@ -16464,9 +16392,6 @@
       <c r="P74" t="n">
         <v>754</v>
       </c>
-      <c r="Q74" t="n">
-        <v>0</v>
-      </c>
       <c r="R74" t="n">
         <v>0.2182808339894617</v>
       </c>
@@ -17118,9 +17043,6 @@
       <c r="P77" t="n">
         <v>812</v>
       </c>
-      <c r="Q77" t="n">
-        <v>0</v>
-      </c>
       <c r="R77" t="n">
         <v>0.2350716673732665</v>
       </c>
@@ -17772,9 +17694,6 @@
       <c r="P80" t="n">
         <v>860</v>
       </c>
-      <c r="Q80" t="n">
-        <v>0</v>
-      </c>
       <c r="R80" t="n">
         <v>0.2489675294840014</v>
       </c>
@@ -18426,9 +18345,6 @@
       <c r="P83" t="n">
         <v>795</v>
       </c>
-      <c r="Q83" t="n">
-        <v>0</v>
-      </c>
       <c r="R83" t="n">
         <v>0.2301502162090478</v>
       </c>
@@ -19080,9 +18996,6 @@
       <c r="P86" t="n">
         <v>599</v>
       </c>
-      <c r="Q86" t="n">
-        <v>0</v>
-      </c>
       <c r="R86" t="n">
         <v>0.17340877925688</v>
       </c>
@@ -19734,9 +19647,6 @@
       <c r="P89" t="n">
         <v>739</v>
       </c>
-      <c r="Q89" t="n">
-        <v>0</v>
-      </c>
       <c r="R89" t="n">
         <v>0.213938377079857</v>
       </c>
@@ -20388,9 +20298,6 @@
       <c r="P92" t="n">
         <v>758</v>
       </c>
-      <c r="Q92" t="n">
-        <v>0</v>
-      </c>
       <c r="R92" t="n">
         <v>0.2194388224986896</v>
       </c>
@@ -21042,9 +20949,6 @@
       <c r="P95" t="n">
         <v>700</v>
       </c>
-      <c r="Q95" t="n">
-        <v>0</v>
-      </c>
       <c r="R95" t="n">
         <v>0.2026479891148849</v>
       </c>
@@ -21696,9 +21600,6 @@
       <c r="P98" t="n">
         <v>700</v>
       </c>
-      <c r="Q98" t="n">
-        <v>0</v>
-      </c>
       <c r="R98" t="n">
         <v>0.2026479891148849</v>
       </c>
@@ -22350,9 +22251,6 @@
       <c r="P101" t="n">
         <v>872</v>
       </c>
-      <c r="Q101" t="n">
-        <v>0</v>
-      </c>
       <c r="R101" t="n">
         <v>0.2524414950116851</v>
       </c>
@@ -23004,9 +22902,6 @@
       <c r="P104" t="n">
         <v>992</v>
       </c>
-      <c r="Q104" t="n">
-        <v>0</v>
-      </c>
       <c r="R104" t="n">
         <v>0.2871811502885225</v>
       </c>
@@ -23658,9 +23553,6 @@
       <c r="P107" t="n">
         <v>618</v>
       </c>
-      <c r="Q107" t="n">
-        <v>0</v>
-      </c>
       <c r="R107" t="n">
         <v>0.1789092246757126</v>
       </c>
@@ -24312,9 +24204,6 @@
       <c r="P110" t="n">
         <v>753</v>
       </c>
-      <c r="Q110" t="n">
-        <v>0</v>
-      </c>
       <c r="R110" t="n">
         <v>0.2179913368621547</v>
       </c>
@@ -24966,9 +24855,6 @@
       <c r="P113" t="n">
         <v>746</v>
       </c>
-      <c r="Q113" t="n">
-        <v>0</v>
-      </c>
       <c r="R113" t="n">
         <v>0.2159648569710059</v>
       </c>
@@ -25620,9 +25506,6 @@
       <c r="P116" t="n">
         <v>790</v>
       </c>
-      <c r="Q116" t="n">
-        <v>0</v>
-      </c>
       <c r="R116" t="n">
         <v>0.2287027305725129</v>
       </c>
@@ -26274,9 +26157,6 @@
       <c r="P119" t="n">
         <v>736</v>
       </c>
-      <c r="Q119" t="n">
-        <v>0</v>
-      </c>
       <c r="R119" t="n">
         <v>0.2130698856979361</v>
       </c>
@@ -26928,9 +26808,6 @@
       <c r="P122" t="n">
         <v>758</v>
       </c>
-      <c r="Q122" t="n">
-        <v>0</v>
-      </c>
       <c r="R122" t="n">
         <v>0.2194388224986896</v>
       </c>
@@ -27582,9 +27459,6 @@
       <c r="P125" t="n">
         <v>768</v>
       </c>
-      <c r="Q125" t="n">
-        <v>0</v>
-      </c>
       <c r="R125" t="n">
         <v>0.2223337937717594</v>
       </c>
@@ -28236,9 +28110,6 @@
       <c r="P128" t="n">
         <v>811</v>
       </c>
-      <c r="Q128" t="n">
-        <v>0</v>
-      </c>
       <c r="R128" t="n">
         <v>0.2347821702459595</v>
       </c>
@@ -28890,9 +28761,6 @@
       <c r="P131" t="n">
         <v>639</v>
       </c>
-      <c r="Q131" t="n">
-        <v>0</v>
-      </c>
       <c r="R131" t="n">
         <v>0.1849886643491592</v>
       </c>
@@ -29544,9 +29412,6 @@
       <c r="P134" t="n">
         <v>497</v>
       </c>
-      <c r="Q134" t="n">
-        <v>0</v>
-      </c>
       <c r="R134" t="n">
         <v>0.1438800722715682</v>
       </c>
@@ -30198,9 +30063,6 @@
       <c r="P137" t="n">
         <v>722</v>
       </c>
-      <c r="Q137" t="n">
-        <v>0</v>
-      </c>
       <c r="R137" t="n">
         <v>0.2090169259156384</v>
       </c>
@@ -30852,9 +30714,6 @@
       <c r="P140" t="n">
         <v>709</v>
       </c>
-      <c r="Q140" t="n">
-        <v>0</v>
-      </c>
       <c r="R140" t="n">
         <v>0.2052534632606477</v>
       </c>
@@ -31506,9 +31365,6 @@
       <c r="P143" t="n">
         <v>477</v>
       </c>
-      <c r="Q143" t="n">
-        <v>0</v>
-      </c>
       <c r="R143" t="n">
         <v>0.1380901297254287</v>
       </c>
@@ -32160,9 +32016,6 @@
       <c r="P146" t="n">
         <v>721</v>
       </c>
-      <c r="Q146" t="n">
-        <v>0</v>
-      </c>
       <c r="R146" t="n">
         <v>0.2087274287883314</v>
       </c>
@@ -32814,9 +32667,6 @@
       <c r="P149" t="n">
         <v>699</v>
       </c>
-      <c r="Q149" t="n">
-        <v>0</v>
-      </c>
       <c r="R149" t="n">
         <v>0.2023584919875779</v>
       </c>
@@ -33468,9 +33318,6 @@
       <c r="P152" t="n">
         <v>736</v>
       </c>
-      <c r="Q152" t="n">
-        <v>0</v>
-      </c>
       <c r="R152" t="n">
         <v>0.2130698856979361</v>
       </c>
@@ -34122,9 +33969,6 @@
       <c r="P155" t="n">
         <v>300</v>
       </c>
-      <c r="Q155" t="n">
-        <v>0</v>
-      </c>
       <c r="R155" t="n">
         <v>0.08684913819209351</v>
       </c>
@@ -34776,9 +34620,6 @@
       <c r="P158" t="n">
         <v>446</v>
       </c>
-      <c r="Q158" t="n">
-        <v>0</v>
-      </c>
       <c r="R158" t="n">
         <v>0.1284281802440269</v>
       </c>
@@ -35430,9 +35271,6 @@
       <c r="P161" t="n">
         <v>530</v>
       </c>
-      <c r="Q161" t="n">
-        <v>0</v>
-      </c>
       <c r="R161" t="n">
         <v>0.152616447375189</v>
       </c>
@@ -36084,9 +35922,6 @@
       <c r="P164" t="n">
         <v>602</v>
       </c>
-      <c r="Q164" t="n">
-        <v>0</v>
-      </c>
       <c r="R164" t="n">
         <v>0.1733492477733278</v>
       </c>
@@ -36738,9 +36573,6 @@
       <c r="P167" t="n">
         <v>660</v>
       </c>
-      <c r="Q167" t="n">
-        <v>0</v>
-      </c>
       <c r="R167" t="n">
         <v>0.190050670316273</v>
       </c>
@@ -37392,9 +37224,6 @@
       <c r="P170" t="n">
         <v>621</v>
       </c>
-      <c r="Q170" t="n">
-        <v>0</v>
-      </c>
       <c r="R170" t="n">
         <v>0.1788204034339478</v>
       </c>
@@ -38046,9 +37875,6 @@
       <c r="P173" t="n">
         <v>813</v>
       </c>
-      <c r="Q173" t="n">
-        <v>0</v>
-      </c>
       <c r="R173" t="n">
         <v>0.2341078711623182</v>
       </c>
@@ -38700,9 +38526,6 @@
       <c r="P176" t="n">
         <v>656</v>
       </c>
-      <c r="Q176" t="n">
-        <v>0</v>
-      </c>
       <c r="R176" t="n">
         <v>0.188898848071932</v>
       </c>
@@ -39354,9 +39177,6 @@
       <c r="P179" t="n">
         <v>709</v>
       </c>
-      <c r="Q179" t="n">
-        <v>0</v>
-      </c>
       <c r="R179" t="n">
         <v>0.2041604928094509</v>
       </c>
@@ -40008,9 +39828,6 @@
       <c r="P182" t="n">
         <v>804</v>
       </c>
-      <c r="Q182" t="n">
-        <v>0</v>
-      </c>
       <c r="R182" t="n">
         <v>0.2315162711125508</v>
       </c>
@@ -40662,9 +40479,6 @@
       <c r="P185" t="n">
         <v>669</v>
       </c>
-      <c r="Q185" t="n">
-        <v>0</v>
-      </c>
       <c r="R185" t="n">
         <v>0.1926422703660404</v>
       </c>
@@ -41316,9 +41130,6 @@
       <c r="P188" t="n">
         <v>635</v>
       </c>
-      <c r="Q188" t="n">
-        <v>0</v>
-      </c>
       <c r="R188" t="n">
         <v>0.1828517812891415</v>
       </c>
@@ -41970,9 +41781,6 @@
       <c r="P191" t="n">
         <v>683</v>
       </c>
-      <c r="Q191" t="n">
-        <v>0</v>
-      </c>
       <c r="R191" t="n">
         <v>0.1966736482212341</v>
       </c>
@@ -42624,9 +42432,6 @@
       <c r="P194" t="n">
         <v>641</v>
       </c>
-      <c r="Q194" t="n">
-        <v>0</v>
-      </c>
       <c r="R194" t="n">
         <v>0.1845795146556531</v>
       </c>
@@ -43278,9 +43083,6 @@
       <c r="P197" t="n">
         <v>604</v>
       </c>
-      <c r="Q197" t="n">
-        <v>0</v>
-      </c>
       <c r="R197" t="n">
         <v>0.1739251588954984</v>
       </c>
@@ -43932,9 +43734,6 @@
       <c r="P200" t="n">
         <v>689</v>
       </c>
-      <c r="Q200" t="n">
-        <v>0</v>
-      </c>
       <c r="R200" t="n">
         <v>0.1984013815877456</v>
       </c>
@@ -44586,9 +44385,6 @@
       <c r="P203" t="n">
         <v>753</v>
       </c>
-      <c r="Q203" t="n">
-        <v>0</v>
-      </c>
       <c r="R203" t="n">
         <v>0.2168305374972024</v>
       </c>
@@ -45240,9 +45036,6 @@
       <c r="P206" t="n">
         <v>666</v>
       </c>
-      <c r="Q206" t="n">
-        <v>0</v>
-      </c>
       <c r="R206" t="n">
         <v>0.1917784036827846</v>
       </c>
@@ -45894,9 +45687,6 @@
       <c r="P209" t="n">
         <v>842</v>
       </c>
-      <c r="Q209" t="n">
-        <v>0</v>
-      </c>
       <c r="R209" t="n">
         <v>0.2424585824337908</v>
       </c>
@@ -46548,9 +46338,6 @@
       <c r="P212" t="n">
         <v>776</v>
       </c>
-      <c r="Q212" t="n">
-        <v>0</v>
-      </c>
       <c r="R212" t="n">
         <v>0.2234535154021635</v>
       </c>
@@ -47202,9 +46989,6 @@
       <c r="P215" t="n">
         <v>862</v>
       </c>
-      <c r="Q215" t="n">
-        <v>0</v>
-      </c>
       <c r="R215" t="n">
         <v>0.248217693655496</v>
       </c>
@@ -47856,9 +47640,6 @@
       <c r="P218" t="n">
         <v>659</v>
       </c>
-      <c r="Q218" t="n">
-        <v>0</v>
-      </c>
       <c r="R218" t="n">
         <v>0.1897627147551878</v>
       </c>
@@ -48510,9 +48291,6 @@
       <c r="P221" t="n">
         <v>538</v>
       </c>
-      <c r="Q221" t="n">
-        <v>0</v>
-      </c>
       <c r="R221" t="n">
         <v>0.1549200918638711</v>
       </c>
@@ -49164,9 +48942,6 @@
       <c r="P224" t="n">
         <v>652</v>
       </c>
-      <c r="Q224" t="n">
-        <v>0</v>
-      </c>
       <c r="R224" t="n">
         <v>0.187747025827591</v>
       </c>
@@ -49818,9 +49593,6 @@
       <c r="P227" t="n">
         <v>630</v>
       </c>
-      <c r="Q227" t="n">
-        <v>0</v>
-      </c>
       <c r="R227" t="n">
         <v>0.1814120034837152</v>
       </c>
@@ -50472,9 +50244,6 @@
       <c r="P230" t="n">
         <v>742</v>
       </c>
-      <c r="Q230" t="n">
-        <v>0</v>
-      </c>
       <c r="R230" t="n">
         <v>0.2136630263252645</v>
       </c>
@@ -51126,9 +50895,6 @@
       <c r="P233" t="n">
         <v>569</v>
       </c>
-      <c r="Q233" t="n">
-        <v>0</v>
-      </c>
       <c r="R233" t="n">
         <v>0.1638467142575142</v>
       </c>
@@ -51780,9 +51546,6 @@
       <c r="P236" t="n">
         <v>475</v>
       </c>
-      <c r="Q236" t="n">
-        <v>0</v>
-      </c>
       <c r="R236" t="n">
         <v>0.1367788915154995</v>
       </c>
@@ -52434,9 +52197,6 @@
       <c r="P239" t="n">
         <v>623</v>
       </c>
-      <c r="Q239" t="n">
-        <v>0</v>
-      </c>
       <c r="R239" t="n">
         <v>0.1793963145561183</v>
       </c>
@@ -53088,9 +52848,6 @@
       <c r="P242" t="n">
         <v>670</v>
       </c>
-      <c r="Q242" t="n">
-        <v>0</v>
-      </c>
       <c r="R242" t="n">
         <v>0.1929302259271257</v>
       </c>
@@ -53742,9 +53499,6 @@
       <c r="P245" t="n">
         <v>584</v>
       </c>
-      <c r="Q245" t="n">
-        <v>0</v>
-      </c>
       <c r="R245" t="n">
         <v>0.1681660476737931</v>
       </c>
@@ -54396,9 +54150,6 @@
       <c r="P248" t="n">
         <v>711</v>
       </c>
-      <c r="Q248" t="n">
-        <v>0</v>
-      </c>
       <c r="R248" t="n">
         <v>0.2047364039316214</v>
       </c>
@@ -55050,9 +54801,6 @@
       <c r="P251" t="n">
         <v>574</v>
       </c>
-      <c r="Q251" t="n">
-        <v>0</v>
-      </c>
       <c r="R251" t="n">
         <v>0.1652864920629405</v>
       </c>
@@ -55704,9 +55452,6 @@
       <c r="P254" t="n">
         <v>757</v>
       </c>
-      <c r="Q254" t="n">
-        <v>0</v>
-      </c>
       <c r="R254" t="n">
         <v>0.2179823597415435</v>
       </c>
@@ -56358,9 +56103,6 @@
       <c r="P257" t="n">
         <v>691</v>
       </c>
-      <c r="Q257" t="n">
-        <v>0</v>
-      </c>
       <c r="R257" t="n">
         <v>0.1989772927099162</v>
       </c>
@@ -57012,9 +56754,6 @@
       <c r="P260" t="n">
         <v>632</v>
       </c>
-      <c r="Q260" t="n">
-        <v>0</v>
-      </c>
       <c r="R260" t="n">
         <v>0.1819879146058857</v>
       </c>
@@ -57666,9 +57405,6 @@
       <c r="P263" t="n">
         <v>590</v>
       </c>
-      <c r="Q263" t="n">
-        <v>0</v>
-      </c>
       <c r="R263" t="n">
         <v>0.1698937810403047</v>
       </c>
@@ -58320,9 +58056,6 @@
       <c r="P266" t="n">
         <v>635</v>
       </c>
-      <c r="Q266" t="n">
-        <v>0</v>
-      </c>
       <c r="R266" t="n">
         <v>0.1828517812891415</v>
       </c>
@@ -58974,9 +58707,6 @@
       <c r="P269" t="n">
         <v>530</v>
       </c>
-      <c r="Q269" t="n">
-        <v>0</v>
-      </c>
       <c r="R269" t="n">
         <v>0.152616447375189</v>
       </c>
@@ -59628,9 +59358,6 @@
       <c r="P272" t="n">
         <v>609</v>
       </c>
-      <c r="Q272" t="n">
-        <v>0</v>
-      </c>
       <c r="R272" t="n">
         <v>0.1753649367009247</v>
       </c>
@@ -60282,9 +60009,6 @@
       <c r="P275" t="n">
         <v>707</v>
       </c>
-      <c r="Q275" t="n">
-        <v>0</v>
-      </c>
       <c r="R275" t="n">
         <v>0.2035845816872804</v>
       </c>
@@ -60936,9 +60660,6 @@
       <c r="P278" t="n">
         <v>640</v>
       </c>
-      <c r="Q278" t="n">
-        <v>0</v>
-      </c>
       <c r="R278" t="n">
         <v>0.1842915590945678</v>
       </c>
@@ -61590,9 +61311,6 @@
       <c r="P281" t="n">
         <v>569</v>
       </c>
-      <c r="Q281" t="n">
-        <v>0</v>
-      </c>
       <c r="R281" t="n">
         <v>0.1638467142575142</v>
       </c>
@@ -62244,9 +61962,6 @@
       <c r="P284" t="n">
         <v>656</v>
       </c>
-      <c r="Q284" t="n">
-        <v>0</v>
-      </c>
       <c r="R284" t="n">
         <v>0.188898848071932</v>
       </c>
@@ -62898,9 +62613,6 @@
       <c r="P287" t="n">
         <v>580</v>
       </c>
-      <c r="Q287" t="n">
-        <v>0</v>
-      </c>
       <c r="R287" t="n">
         <v>0.1670142254294521</v>
       </c>
@@ -63552,9 +63264,6 @@
       <c r="P290" t="n">
         <v>647</v>
       </c>
-      <c r="Q290" t="n">
-        <v>0</v>
-      </c>
       <c r="R290" t="n">
         <v>0.1863072480221646</v>
       </c>
@@ -64206,9 +63915,6 @@
       <c r="P293" t="n">
         <v>629</v>
       </c>
-      <c r="Q293" t="n">
-        <v>0</v>
-      </c>
       <c r="R293" t="n">
         <v>0.1811240479226299</v>
       </c>
@@ -64860,9 +64566,6 @@
       <c r="P296" t="n">
         <v>672</v>
       </c>
-      <c r="Q296" t="n">
-        <v>0</v>
-      </c>
       <c r="R296" t="n">
         <v>0.1935061370492962</v>
       </c>
@@ -65514,9 +65217,6 @@
       <c r="P299" t="n">
         <v>447</v>
       </c>
-      <c r="Q299" t="n">
-        <v>0</v>
-      </c>
       <c r="R299" t="n">
         <v>0.1287161358051122</v>
       </c>
@@ -66168,9 +65868,6 @@
       <c r="P302" t="n">
         <v>497</v>
       </c>
-      <c r="Q302" t="n">
-        <v>0</v>
-      </c>
       <c r="R302" t="n">
         <v>0.1431139138593753</v>
       </c>
@@ -66822,9 +66519,6 @@
       <c r="P305" t="n">
         <v>528</v>
       </c>
-      <c r="Q305" t="n">
-        <v>0</v>
-      </c>
       <c r="R305" t="n">
         <v>0.1520405362530184</v>
       </c>
@@ -67476,9 +67170,6 @@
       <c r="P308" t="n">
         <v>850</v>
       </c>
-      <c r="Q308" t="n">
-        <v>0</v>
-      </c>
       <c r="R308" t="n">
         <v>0.2447622269224729</v>
       </c>
@@ -68129,9 +67820,6 @@
       </c>
       <c r="P311" t="n">
         <v>439</v>
-      </c>
-      <c r="Q311" t="n">
-        <v>0</v>
       </c>
       <c r="R311" t="n">
         <v>0.1264124913164301</v>

--- a/diseases/d211/2020-2025.xlsx
+++ b/diseases/d211/2020-2025.xlsx
@@ -1012,7 +1012,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1254,7 +1254,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
@@ -1663,7 +1663,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
@@ -1905,7 +1905,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2314,7 +2314,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2556,7 +2556,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
@@ -2965,7 +2965,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
@@ -3207,7 +3207,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3616,7 +3616,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
@@ -4267,7 +4267,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
@@ -4509,7 +4509,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4918,7 +4918,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -5160,7 +5160,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
@@ -5569,7 +5569,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
@@ -5811,7 +5811,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -6220,7 +6220,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -6462,7 +6462,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
@@ -6871,7 +6871,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
@@ -7113,7 +7113,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -7522,7 +7522,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7764,7 +7764,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
@@ -8173,7 +8173,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
@@ -8415,7 +8415,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -8824,7 +8824,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -9066,7 +9066,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK40" t="inlineStr">
@@ -9475,7 +9475,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
@@ -9717,7 +9717,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -10126,7 +10126,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -10368,7 +10368,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
@@ -10777,7 +10777,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK48" t="inlineStr">
@@ -11019,7 +11019,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -11428,7 +11428,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -11670,7 +11670,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK52" t="inlineStr">
@@ -12079,7 +12079,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK54" t="inlineStr">
@@ -12321,7 +12321,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -12730,7 +12730,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -12972,7 +12972,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK58" t="inlineStr">
@@ -13381,7 +13381,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK60" t="inlineStr">
@@ -13623,7 +13623,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -14032,7 +14032,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -14274,7 +14274,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK64" t="inlineStr">
@@ -14683,7 +14683,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK66" t="inlineStr">
@@ -14925,7 +14925,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -15334,7 +15334,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -15576,7 +15576,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK70" t="inlineStr">
@@ -15985,7 +15985,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK72" t="inlineStr">
@@ -16227,7 +16227,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -16636,7 +16636,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -16878,7 +16878,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK76" t="inlineStr">
@@ -17287,7 +17287,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK78" t="inlineStr">
@@ -17529,7 +17529,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -17938,7 +17938,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -18180,7 +18180,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK82" t="inlineStr">
@@ -18589,7 +18589,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK84" t="inlineStr">
@@ -18831,7 +18831,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -19240,7 +19240,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -19482,7 +19482,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK88" t="inlineStr">
@@ -19891,7 +19891,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK90" t="inlineStr">
@@ -20133,7 +20133,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -20542,7 +20542,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -20784,7 +20784,7 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK94" t="inlineStr">
@@ -21193,7 +21193,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK96" t="inlineStr">
@@ -21435,7 +21435,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
@@ -21844,7 +21844,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -22086,7 +22086,7 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK100" t="inlineStr">
@@ -22495,7 +22495,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK102" t="inlineStr">
@@ -22737,7 +22737,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -23146,7 +23146,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
@@ -23388,7 +23388,7 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK106" t="inlineStr">
@@ -23797,7 +23797,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK108" t="inlineStr">
@@ -24039,7 +24039,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
@@ -24448,7 +24448,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -24690,7 +24690,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK112" t="inlineStr">
@@ -25099,7 +25099,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK114" t="inlineStr">
@@ -25341,7 +25341,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
@@ -25750,7 +25750,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK117" t="inlineStr">
@@ -25992,7 +25992,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK118" t="inlineStr">
@@ -26401,7 +26401,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK120" t="inlineStr">
@@ -26643,7 +26643,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK121" t="inlineStr">
@@ -27052,7 +27052,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
@@ -27294,7 +27294,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK124" t="inlineStr">
@@ -27703,7 +27703,7 @@
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK126" t="inlineStr">
@@ -27945,7 +27945,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK127" t="inlineStr">
@@ -28354,7 +28354,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK129" t="inlineStr">
@@ -28596,7 +28596,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK130" t="inlineStr">
@@ -29005,7 +29005,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK132" t="inlineStr">
@@ -29247,7 +29247,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK133" t="inlineStr">
@@ -29656,7 +29656,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
@@ -29898,7 +29898,7 @@
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK136" t="inlineStr">
@@ -30307,7 +30307,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK138" t="inlineStr">
@@ -30549,7 +30549,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK139" t="inlineStr">
@@ -30958,7 +30958,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK141" t="inlineStr">
@@ -31200,7 +31200,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK142" t="inlineStr">
@@ -31609,7 +31609,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK144" t="inlineStr">
@@ -31851,7 +31851,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK145" t="inlineStr">
@@ -32260,7 +32260,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">
@@ -32502,7 +32502,7 @@
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK148" t="inlineStr">
@@ -32911,7 +32911,7 @@
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK150" t="inlineStr">
@@ -33153,7 +33153,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK151" t="inlineStr">
@@ -33562,7 +33562,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK153" t="inlineStr">
@@ -33804,7 +33804,7 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK154" t="inlineStr">
@@ -34213,7 +34213,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK156" t="inlineStr">
@@ -34455,7 +34455,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK157" t="inlineStr">
@@ -34864,7 +34864,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK159" t="inlineStr">
@@ -35106,7 +35106,7 @@
       </c>
       <c r="AJ160" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK160" t="inlineStr">
@@ -35515,7 +35515,7 @@
       </c>
       <c r="AJ162" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK162" t="inlineStr">
@@ -35757,7 +35757,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK163" t="inlineStr">
@@ -36166,7 +36166,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK165" t="inlineStr">
@@ -36408,7 +36408,7 @@
       </c>
       <c r="AJ166" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK166" t="inlineStr">
@@ -36817,7 +36817,7 @@
       </c>
       <c r="AJ168" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK168" t="inlineStr">
@@ -37059,7 +37059,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK169" t="inlineStr">
@@ -37468,7 +37468,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK171" t="inlineStr">
@@ -37710,7 +37710,7 @@
       </c>
       <c r="AJ172" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK172" t="inlineStr">
@@ -38119,7 +38119,7 @@
       </c>
       <c r="AJ174" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK174" t="inlineStr">
@@ -38361,7 +38361,7 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK175" t="inlineStr">
@@ -38770,7 +38770,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK177" t="inlineStr">
@@ -39012,7 +39012,7 @@
       </c>
       <c r="AJ178" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK178" t="inlineStr">
@@ -39421,7 +39421,7 @@
       </c>
       <c r="AJ180" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK180" t="inlineStr">
@@ -39663,7 +39663,7 @@
       </c>
       <c r="AJ181" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK181" t="inlineStr">
@@ -40072,7 +40072,7 @@
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK183" t="inlineStr">
@@ -40314,7 +40314,7 @@
       </c>
       <c r="AJ184" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK184" t="inlineStr">
@@ -40723,7 +40723,7 @@
       </c>
       <c r="AJ186" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK186" t="inlineStr">
@@ -40965,7 +40965,7 @@
       </c>
       <c r="AJ187" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK187" t="inlineStr">
@@ -41374,7 +41374,7 @@
       </c>
       <c r="AJ189" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK189" t="inlineStr">
@@ -41616,7 +41616,7 @@
       </c>
       <c r="AJ190" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK190" t="inlineStr">
@@ -42025,7 +42025,7 @@
       </c>
       <c r="AJ192" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK192" t="inlineStr">
@@ -42267,7 +42267,7 @@
       </c>
       <c r="AJ193" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK193" t="inlineStr">
@@ -42676,7 +42676,7 @@
       </c>
       <c r="AJ195" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK195" t="inlineStr">
@@ -42918,7 +42918,7 @@
       </c>
       <c r="AJ196" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK196" t="inlineStr">
@@ -43327,7 +43327,7 @@
       </c>
       <c r="AJ198" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK198" t="inlineStr">
@@ -43569,7 +43569,7 @@
       </c>
       <c r="AJ199" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK199" t="inlineStr">
@@ -43978,7 +43978,7 @@
       </c>
       <c r="AJ201" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK201" t="inlineStr">
@@ -44220,7 +44220,7 @@
       </c>
       <c r="AJ202" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK202" t="inlineStr">
@@ -44629,7 +44629,7 @@
       </c>
       <c r="AJ204" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK204" t="inlineStr">
@@ -44871,7 +44871,7 @@
       </c>
       <c r="AJ205" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK205" t="inlineStr">
@@ -45280,7 +45280,7 @@
       </c>
       <c r="AJ207" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK207" t="inlineStr">
@@ -45522,7 +45522,7 @@
       </c>
       <c r="AJ208" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK208" t="inlineStr">
@@ -45931,7 +45931,7 @@
       </c>
       <c r="AJ210" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK210" t="inlineStr">
@@ -46173,7 +46173,7 @@
       </c>
       <c r="AJ211" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK211" t="inlineStr">
@@ -46582,7 +46582,7 @@
       </c>
       <c r="AJ213" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK213" t="inlineStr">
@@ -46824,7 +46824,7 @@
       </c>
       <c r="AJ214" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK214" t="inlineStr">
@@ -47233,7 +47233,7 @@
       </c>
       <c r="AJ216" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK216" t="inlineStr">
@@ -47475,7 +47475,7 @@
       </c>
       <c r="AJ217" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK217" t="inlineStr">
@@ -47884,7 +47884,7 @@
       </c>
       <c r="AJ219" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK219" t="inlineStr">
@@ -48126,7 +48126,7 @@
       </c>
       <c r="AJ220" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK220" t="inlineStr">
@@ -48535,7 +48535,7 @@
       </c>
       <c r="AJ222" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK222" t="inlineStr">
@@ -48777,7 +48777,7 @@
       </c>
       <c r="AJ223" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK223" t="inlineStr">
@@ -49186,7 +49186,7 @@
       </c>
       <c r="AJ225" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK225" t="inlineStr">
@@ -49428,7 +49428,7 @@
       </c>
       <c r="AJ226" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK226" t="inlineStr">
@@ -49837,7 +49837,7 @@
       </c>
       <c r="AJ228" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK228" t="inlineStr">
@@ -50079,7 +50079,7 @@
       </c>
       <c r="AJ229" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK229" t="inlineStr">
@@ -50488,7 +50488,7 @@
       </c>
       <c r="AJ231" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK231" t="inlineStr">
@@ -50730,7 +50730,7 @@
       </c>
       <c r="AJ232" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK232" t="inlineStr">
@@ -51139,7 +51139,7 @@
       </c>
       <c r="AJ234" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK234" t="inlineStr">
@@ -51381,7 +51381,7 @@
       </c>
       <c r="AJ235" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK235" t="inlineStr">
@@ -51790,7 +51790,7 @@
       </c>
       <c r="AJ237" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK237" t="inlineStr">
@@ -52032,7 +52032,7 @@
       </c>
       <c r="AJ238" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK238" t="inlineStr">
@@ -52441,7 +52441,7 @@
       </c>
       <c r="AJ240" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK240" t="inlineStr">
@@ -52683,7 +52683,7 @@
       </c>
       <c r="AJ241" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK241" t="inlineStr">
@@ -53092,7 +53092,7 @@
       </c>
       <c r="AJ243" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK243" t="inlineStr">
@@ -53334,7 +53334,7 @@
       </c>
       <c r="AJ244" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK244" t="inlineStr">
@@ -53743,7 +53743,7 @@
       </c>
       <c r="AJ246" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK246" t="inlineStr">
@@ -53985,7 +53985,7 @@
       </c>
       <c r="AJ247" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK247" t="inlineStr">
@@ -54394,7 +54394,7 @@
       </c>
       <c r="AJ249" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK249" t="inlineStr">
@@ -54636,7 +54636,7 @@
       </c>
       <c r="AJ250" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK250" t="inlineStr">
@@ -55045,7 +55045,7 @@
       </c>
       <c r="AJ252" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK252" t="inlineStr">
@@ -55287,7 +55287,7 @@
       </c>
       <c r="AJ253" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK253" t="inlineStr">
@@ -55696,7 +55696,7 @@
       </c>
       <c r="AJ255" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK255" t="inlineStr">
@@ -55938,7 +55938,7 @@
       </c>
       <c r="AJ256" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK256" t="inlineStr">
@@ -56347,7 +56347,7 @@
       </c>
       <c r="AJ258" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK258" t="inlineStr">
@@ -56589,7 +56589,7 @@
       </c>
       <c r="AJ259" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK259" t="inlineStr">
@@ -56998,7 +56998,7 @@
       </c>
       <c r="AJ261" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK261" t="inlineStr">
@@ -57240,7 +57240,7 @@
       </c>
       <c r="AJ262" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK262" t="inlineStr">
@@ -57649,7 +57649,7 @@
       </c>
       <c r="AJ264" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK264" t="inlineStr">
@@ -57891,7 +57891,7 @@
       </c>
       <c r="AJ265" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK265" t="inlineStr">
@@ -58300,7 +58300,7 @@
       </c>
       <c r="AJ267" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK267" t="inlineStr">
@@ -58542,7 +58542,7 @@
       </c>
       <c r="AJ268" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK268" t="inlineStr">
@@ -58951,7 +58951,7 @@
       </c>
       <c r="AJ270" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK270" t="inlineStr">
@@ -59193,7 +59193,7 @@
       </c>
       <c r="AJ271" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK271" t="inlineStr">
@@ -59602,7 +59602,7 @@
       </c>
       <c r="AJ273" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK273" t="inlineStr">
@@ -59844,7 +59844,7 @@
       </c>
       <c r="AJ274" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK274" t="inlineStr">
@@ -60253,7 +60253,7 @@
       </c>
       <c r="AJ276" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK276" t="inlineStr">
@@ -60495,7 +60495,7 @@
       </c>
       <c r="AJ277" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK277" t="inlineStr">
@@ -60904,7 +60904,7 @@
       </c>
       <c r="AJ279" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK279" t="inlineStr">
@@ -61146,7 +61146,7 @@
       </c>
       <c r="AJ280" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK280" t="inlineStr">
@@ -61555,7 +61555,7 @@
       </c>
       <c r="AJ282" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK282" t="inlineStr">
@@ -61797,7 +61797,7 @@
       </c>
       <c r="AJ283" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK283" t="inlineStr">
@@ -62206,7 +62206,7 @@
       </c>
       <c r="AJ285" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK285" t="inlineStr">
@@ -62448,7 +62448,7 @@
       </c>
       <c r="AJ286" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK286" t="inlineStr">
@@ -62857,7 +62857,7 @@
       </c>
       <c r="AJ288" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK288" t="inlineStr">
@@ -63099,7 +63099,7 @@
       </c>
       <c r="AJ289" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK289" t="inlineStr">
@@ -63508,7 +63508,7 @@
       </c>
       <c r="AJ291" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK291" t="inlineStr">
@@ -63750,7 +63750,7 @@
       </c>
       <c r="AJ292" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK292" t="inlineStr">
@@ -64159,7 +64159,7 @@
       </c>
       <c r="AJ294" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK294" t="inlineStr">
@@ -64401,7 +64401,7 @@
       </c>
       <c r="AJ295" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK295" t="inlineStr">
@@ -64810,7 +64810,7 @@
       </c>
       <c r="AJ297" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK297" t="inlineStr">
@@ -65052,7 +65052,7 @@
       </c>
       <c r="AJ298" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK298" t="inlineStr">
@@ -65461,7 +65461,7 @@
       </c>
       <c r="AJ300" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK300" t="inlineStr">
@@ -65703,7 +65703,7 @@
       </c>
       <c r="AJ301" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK301" t="inlineStr">
@@ -66112,7 +66112,7 @@
       </c>
       <c r="AJ303" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK303" t="inlineStr">
@@ -66354,7 +66354,7 @@
       </c>
       <c r="AJ304" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK304" t="inlineStr">
@@ -66763,7 +66763,7 @@
       </c>
       <c r="AJ306" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK306" t="inlineStr">
@@ -67005,7 +67005,7 @@
       </c>
       <c r="AJ307" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK307" t="inlineStr">
@@ -67414,7 +67414,7 @@
       </c>
       <c r="AJ309" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK309" t="inlineStr">
@@ -67656,7 +67656,7 @@
       </c>
       <c r="AJ310" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK310" t="inlineStr">
@@ -68065,7 +68065,7 @@
       </c>
       <c r="AJ312" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK312" t="inlineStr">
@@ -68307,7 +68307,7 @@
       </c>
       <c r="AJ313" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK313" t="inlineStr">

--- a/diseases/d211/2020-2025.xlsx
+++ b/diseases/d211/2020-2025.xlsx
@@ -1012,7 +1012,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1254,7 +1254,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
@@ -1663,7 +1663,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
@@ -1905,7 +1905,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2314,7 +2314,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2556,7 +2556,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
@@ -2965,7 +2965,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
@@ -3207,7 +3207,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3616,7 +3616,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
@@ -4267,7 +4267,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
@@ -4509,7 +4509,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4918,7 +4918,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -5160,7 +5160,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
@@ -5569,7 +5569,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
@@ -5811,7 +5811,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -6220,7 +6220,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -6462,7 +6462,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
@@ -6871,7 +6871,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
@@ -7113,7 +7113,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -7522,7 +7522,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7764,7 +7764,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
@@ -8173,7 +8173,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
@@ -8415,7 +8415,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -8824,7 +8824,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -9066,7 +9066,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK40" t="inlineStr">
@@ -9475,7 +9475,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
@@ -9717,7 +9717,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -10126,7 +10126,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -10368,7 +10368,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
@@ -10777,7 +10777,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK48" t="inlineStr">
@@ -11019,7 +11019,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -11428,7 +11428,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -11670,7 +11670,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK52" t="inlineStr">
@@ -12079,7 +12079,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK54" t="inlineStr">
@@ -12321,7 +12321,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -12730,7 +12730,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -12972,7 +12972,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK58" t="inlineStr">
@@ -13381,7 +13381,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK60" t="inlineStr">
@@ -13623,7 +13623,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -14032,7 +14032,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -14274,7 +14274,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK64" t="inlineStr">
@@ -14683,7 +14683,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK66" t="inlineStr">
@@ -14925,7 +14925,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -15334,7 +15334,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -15576,7 +15576,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK70" t="inlineStr">
@@ -15985,7 +15985,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK72" t="inlineStr">
@@ -16227,7 +16227,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -16636,7 +16636,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -16878,7 +16878,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK76" t="inlineStr">
@@ -17287,7 +17287,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK78" t="inlineStr">
@@ -17529,7 +17529,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -17938,7 +17938,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -18180,7 +18180,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK82" t="inlineStr">
@@ -18589,7 +18589,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK84" t="inlineStr">
@@ -18831,7 +18831,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -19240,7 +19240,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -19482,7 +19482,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK88" t="inlineStr">
@@ -19891,7 +19891,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK90" t="inlineStr">
@@ -20133,7 +20133,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -20542,7 +20542,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -20784,7 +20784,7 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK94" t="inlineStr">
@@ -21193,7 +21193,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK96" t="inlineStr">
@@ -21435,7 +21435,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
@@ -21844,7 +21844,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -22086,7 +22086,7 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK100" t="inlineStr">
@@ -22495,7 +22495,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK102" t="inlineStr">
@@ -22737,7 +22737,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -23146,7 +23146,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
@@ -23388,7 +23388,7 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK106" t="inlineStr">
@@ -23797,7 +23797,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK108" t="inlineStr">
@@ -24039,7 +24039,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
@@ -24448,7 +24448,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -24690,7 +24690,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK112" t="inlineStr">
@@ -25099,7 +25099,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK114" t="inlineStr">
@@ -25341,7 +25341,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
@@ -25750,7 +25750,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK117" t="inlineStr">
@@ -25992,7 +25992,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK118" t="inlineStr">
@@ -26401,7 +26401,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK120" t="inlineStr">
@@ -26643,7 +26643,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK121" t="inlineStr">
@@ -27052,7 +27052,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
@@ -27294,7 +27294,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK124" t="inlineStr">
@@ -27703,7 +27703,7 @@
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK126" t="inlineStr">
@@ -27945,7 +27945,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK127" t="inlineStr">
@@ -28354,7 +28354,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK129" t="inlineStr">
@@ -28596,7 +28596,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK130" t="inlineStr">
@@ -29005,7 +29005,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK132" t="inlineStr">
@@ -29247,7 +29247,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK133" t="inlineStr">
@@ -29656,7 +29656,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
@@ -29898,7 +29898,7 @@
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK136" t="inlineStr">
@@ -30307,7 +30307,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK138" t="inlineStr">
@@ -30549,7 +30549,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK139" t="inlineStr">
@@ -30958,7 +30958,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK141" t="inlineStr">
@@ -31200,7 +31200,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK142" t="inlineStr">
@@ -31609,7 +31609,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK144" t="inlineStr">
@@ -31851,7 +31851,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK145" t="inlineStr">
@@ -32260,7 +32260,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">
@@ -32502,7 +32502,7 @@
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK148" t="inlineStr">
@@ -32911,7 +32911,7 @@
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK150" t="inlineStr">
@@ -33153,7 +33153,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK151" t="inlineStr">
@@ -33562,7 +33562,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK153" t="inlineStr">
@@ -33804,7 +33804,7 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK154" t="inlineStr">
@@ -34213,7 +34213,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK156" t="inlineStr">
@@ -34455,7 +34455,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK157" t="inlineStr">
@@ -34864,7 +34864,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK159" t="inlineStr">
@@ -35106,7 +35106,7 @@
       </c>
       <c r="AJ160" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK160" t="inlineStr">
@@ -35515,7 +35515,7 @@
       </c>
       <c r="AJ162" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK162" t="inlineStr">
@@ -35757,7 +35757,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK163" t="inlineStr">
@@ -36166,7 +36166,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK165" t="inlineStr">
@@ -36408,7 +36408,7 @@
       </c>
       <c r="AJ166" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK166" t="inlineStr">
@@ -36817,7 +36817,7 @@
       </c>
       <c r="AJ168" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK168" t="inlineStr">
@@ -37059,7 +37059,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK169" t="inlineStr">
@@ -37468,7 +37468,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK171" t="inlineStr">
@@ -37710,7 +37710,7 @@
       </c>
       <c r="AJ172" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK172" t="inlineStr">
@@ -38119,7 +38119,7 @@
       </c>
       <c r="AJ174" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK174" t="inlineStr">
@@ -38361,7 +38361,7 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK175" t="inlineStr">
@@ -38770,7 +38770,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK177" t="inlineStr">
@@ -39012,7 +39012,7 @@
       </c>
       <c r="AJ178" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK178" t="inlineStr">
@@ -39421,7 +39421,7 @@
       </c>
       <c r="AJ180" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK180" t="inlineStr">
@@ -39663,7 +39663,7 @@
       </c>
       <c r="AJ181" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK181" t="inlineStr">
@@ -40072,7 +40072,7 @@
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK183" t="inlineStr">
@@ -40314,7 +40314,7 @@
       </c>
       <c r="AJ184" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK184" t="inlineStr">
@@ -40723,7 +40723,7 @@
       </c>
       <c r="AJ186" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK186" t="inlineStr">
@@ -40965,7 +40965,7 @@
       </c>
       <c r="AJ187" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK187" t="inlineStr">
@@ -41374,7 +41374,7 @@
       </c>
       <c r="AJ189" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK189" t="inlineStr">
@@ -41616,7 +41616,7 @@
       </c>
       <c r="AJ190" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK190" t="inlineStr">
@@ -42025,7 +42025,7 @@
       </c>
       <c r="AJ192" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK192" t="inlineStr">
@@ -42267,7 +42267,7 @@
       </c>
       <c r="AJ193" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK193" t="inlineStr">
@@ -42676,7 +42676,7 @@
       </c>
       <c r="AJ195" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK195" t="inlineStr">
@@ -42918,7 +42918,7 @@
       </c>
       <c r="AJ196" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK196" t="inlineStr">
@@ -43327,7 +43327,7 @@
       </c>
       <c r="AJ198" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK198" t="inlineStr">
@@ -43569,7 +43569,7 @@
       </c>
       <c r="AJ199" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK199" t="inlineStr">
@@ -43978,7 +43978,7 @@
       </c>
       <c r="AJ201" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK201" t="inlineStr">
@@ -44220,7 +44220,7 @@
       </c>
       <c r="AJ202" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK202" t="inlineStr">
@@ -44629,7 +44629,7 @@
       </c>
       <c r="AJ204" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK204" t="inlineStr">
@@ -44871,7 +44871,7 @@
       </c>
       <c r="AJ205" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK205" t="inlineStr">
@@ -45280,7 +45280,7 @@
       </c>
       <c r="AJ207" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK207" t="inlineStr">
@@ -45522,7 +45522,7 @@
       </c>
       <c r="AJ208" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK208" t="inlineStr">
@@ -45931,7 +45931,7 @@
       </c>
       <c r="AJ210" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK210" t="inlineStr">
@@ -46173,7 +46173,7 @@
       </c>
       <c r="AJ211" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK211" t="inlineStr">
@@ -46582,7 +46582,7 @@
       </c>
       <c r="AJ213" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK213" t="inlineStr">
@@ -46824,7 +46824,7 @@
       </c>
       <c r="AJ214" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK214" t="inlineStr">
@@ -47233,7 +47233,7 @@
       </c>
       <c r="AJ216" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK216" t="inlineStr">
@@ -47475,7 +47475,7 @@
       </c>
       <c r="AJ217" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK217" t="inlineStr">
@@ -47884,7 +47884,7 @@
       </c>
       <c r="AJ219" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK219" t="inlineStr">
@@ -48126,7 +48126,7 @@
       </c>
       <c r="AJ220" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK220" t="inlineStr">
@@ -48535,7 +48535,7 @@
       </c>
       <c r="AJ222" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK222" t="inlineStr">
@@ -48777,7 +48777,7 @@
       </c>
       <c r="AJ223" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK223" t="inlineStr">
@@ -49186,7 +49186,7 @@
       </c>
       <c r="AJ225" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK225" t="inlineStr">
@@ -49428,7 +49428,7 @@
       </c>
       <c r="AJ226" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK226" t="inlineStr">
@@ -49837,7 +49837,7 @@
       </c>
       <c r="AJ228" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK228" t="inlineStr">
@@ -50079,7 +50079,7 @@
       </c>
       <c r="AJ229" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK229" t="inlineStr">
@@ -50488,7 +50488,7 @@
       </c>
       <c r="AJ231" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK231" t="inlineStr">
@@ -50730,7 +50730,7 @@
       </c>
       <c r="AJ232" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK232" t="inlineStr">
@@ -51139,7 +51139,7 @@
       </c>
       <c r="AJ234" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK234" t="inlineStr">
@@ -51381,7 +51381,7 @@
       </c>
       <c r="AJ235" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK235" t="inlineStr">
@@ -51790,7 +51790,7 @@
       </c>
       <c r="AJ237" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK237" t="inlineStr">
@@ -52032,7 +52032,7 @@
       </c>
       <c r="AJ238" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK238" t="inlineStr">
@@ -52441,7 +52441,7 @@
       </c>
       <c r="AJ240" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK240" t="inlineStr">
@@ -52683,7 +52683,7 @@
       </c>
       <c r="AJ241" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK241" t="inlineStr">
@@ -53092,7 +53092,7 @@
       </c>
       <c r="AJ243" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK243" t="inlineStr">
@@ -53334,7 +53334,7 @@
       </c>
       <c r="AJ244" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK244" t="inlineStr">
@@ -53743,7 +53743,7 @@
       </c>
       <c r="AJ246" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK246" t="inlineStr">
@@ -53985,7 +53985,7 @@
       </c>
       <c r="AJ247" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK247" t="inlineStr">
@@ -54394,7 +54394,7 @@
       </c>
       <c r="AJ249" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK249" t="inlineStr">
@@ -54636,7 +54636,7 @@
       </c>
       <c r="AJ250" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK250" t="inlineStr">
@@ -55045,7 +55045,7 @@
       </c>
       <c r="AJ252" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK252" t="inlineStr">
@@ -55287,7 +55287,7 @@
       </c>
       <c r="AJ253" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK253" t="inlineStr">
@@ -55696,7 +55696,7 @@
       </c>
       <c r="AJ255" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK255" t="inlineStr">
@@ -55938,7 +55938,7 @@
       </c>
       <c r="AJ256" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK256" t="inlineStr">
@@ -56347,7 +56347,7 @@
       </c>
       <c r="AJ258" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK258" t="inlineStr">
@@ -56589,7 +56589,7 @@
       </c>
       <c r="AJ259" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK259" t="inlineStr">
@@ -56998,7 +56998,7 @@
       </c>
       <c r="AJ261" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK261" t="inlineStr">
@@ -57240,7 +57240,7 @@
       </c>
       <c r="AJ262" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK262" t="inlineStr">
@@ -57649,7 +57649,7 @@
       </c>
       <c r="AJ264" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK264" t="inlineStr">
@@ -57891,7 +57891,7 @@
       </c>
       <c r="AJ265" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK265" t="inlineStr">
@@ -58300,7 +58300,7 @@
       </c>
       <c r="AJ267" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK267" t="inlineStr">
@@ -58542,7 +58542,7 @@
       </c>
       <c r="AJ268" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK268" t="inlineStr">
@@ -58951,7 +58951,7 @@
       </c>
       <c r="AJ270" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK270" t="inlineStr">
@@ -59193,7 +59193,7 @@
       </c>
       <c r="AJ271" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK271" t="inlineStr">
@@ -59602,7 +59602,7 @@
       </c>
       <c r="AJ273" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK273" t="inlineStr">
@@ -59844,7 +59844,7 @@
       </c>
       <c r="AJ274" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK274" t="inlineStr">
@@ -60253,7 +60253,7 @@
       </c>
       <c r="AJ276" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK276" t="inlineStr">
@@ -60495,7 +60495,7 @@
       </c>
       <c r="AJ277" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK277" t="inlineStr">
@@ -60904,7 +60904,7 @@
       </c>
       <c r="AJ279" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK279" t="inlineStr">
@@ -61146,7 +61146,7 @@
       </c>
       <c r="AJ280" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK280" t="inlineStr">
@@ -61555,7 +61555,7 @@
       </c>
       <c r="AJ282" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK282" t="inlineStr">
@@ -61797,7 +61797,7 @@
       </c>
       <c r="AJ283" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK283" t="inlineStr">
@@ -62206,7 +62206,7 @@
       </c>
       <c r="AJ285" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK285" t="inlineStr">
@@ -62448,7 +62448,7 @@
       </c>
       <c r="AJ286" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK286" t="inlineStr">
@@ -62857,7 +62857,7 @@
       </c>
       <c r="AJ288" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK288" t="inlineStr">
@@ -63099,7 +63099,7 @@
       </c>
       <c r="AJ289" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK289" t="inlineStr">
@@ -63508,7 +63508,7 @@
       </c>
       <c r="AJ291" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK291" t="inlineStr">
@@ -63750,7 +63750,7 @@
       </c>
       <c r="AJ292" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK292" t="inlineStr">
@@ -64159,7 +64159,7 @@
       </c>
       <c r="AJ294" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK294" t="inlineStr">
@@ -64401,7 +64401,7 @@
       </c>
       <c r="AJ295" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK295" t="inlineStr">
@@ -64810,7 +64810,7 @@
       </c>
       <c r="AJ297" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK297" t="inlineStr">
@@ -65052,7 +65052,7 @@
       </c>
       <c r="AJ298" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK298" t="inlineStr">
@@ -65461,7 +65461,7 @@
       </c>
       <c r="AJ300" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK300" t="inlineStr">
@@ -65703,7 +65703,7 @@
       </c>
       <c r="AJ301" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK301" t="inlineStr">
@@ -66112,7 +66112,7 @@
       </c>
       <c r="AJ303" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK303" t="inlineStr">
@@ -66354,7 +66354,7 @@
       </c>
       <c r="AJ304" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK304" t="inlineStr">
@@ -66763,7 +66763,7 @@
       </c>
       <c r="AJ306" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK306" t="inlineStr">
@@ -67005,7 +67005,7 @@
       </c>
       <c r="AJ307" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK307" t="inlineStr">
@@ -67414,7 +67414,7 @@
       </c>
       <c r="AJ309" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK309" t="inlineStr">
@@ -67656,7 +67656,7 @@
       </c>
       <c r="AJ310" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK310" t="inlineStr">
@@ -68065,7 +68065,7 @@
       </c>
       <c r="AJ312" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK312" t="inlineStr">
@@ -68307,7 +68307,7 @@
       </c>
       <c r="AJ313" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK313" t="inlineStr">

--- a/diseases/d211/2020-2025.xlsx
+++ b/diseases/d211/2020-2025.xlsx
@@ -1012,7 +1012,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1254,7 +1254,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
@@ -1663,7 +1663,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
@@ -1905,7 +1905,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2314,7 +2314,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2556,7 +2556,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
@@ -2965,7 +2965,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
@@ -3207,7 +3207,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3616,7 +3616,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
@@ -4267,7 +4267,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
@@ -4509,7 +4509,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4918,7 +4918,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -5160,7 +5160,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
@@ -5569,7 +5569,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
@@ -5811,7 +5811,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -6220,7 +6220,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -6462,7 +6462,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
@@ -6871,7 +6871,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
@@ -7113,7 +7113,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -7522,7 +7522,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7764,7 +7764,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
@@ -8173,7 +8173,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
@@ -8415,7 +8415,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -8824,7 +8824,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -9066,7 +9066,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK40" t="inlineStr">
@@ -9475,7 +9475,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
@@ -9717,7 +9717,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -10126,7 +10126,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -10368,7 +10368,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
@@ -10777,7 +10777,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK48" t="inlineStr">
@@ -11019,7 +11019,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -11428,7 +11428,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -11670,7 +11670,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK52" t="inlineStr">
@@ -12079,7 +12079,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK54" t="inlineStr">
@@ -12321,7 +12321,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -12730,7 +12730,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -12972,7 +12972,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK58" t="inlineStr">
@@ -13381,7 +13381,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK60" t="inlineStr">
@@ -13623,7 +13623,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -14032,7 +14032,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -14274,7 +14274,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK64" t="inlineStr">
@@ -14683,7 +14683,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK66" t="inlineStr">
@@ -14925,7 +14925,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -15334,7 +15334,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -15576,7 +15576,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK70" t="inlineStr">
@@ -15985,7 +15985,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK72" t="inlineStr">
@@ -16227,7 +16227,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -16636,7 +16636,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -16878,7 +16878,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK76" t="inlineStr">
@@ -17287,7 +17287,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK78" t="inlineStr">
@@ -17529,7 +17529,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -17938,7 +17938,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -18180,7 +18180,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK82" t="inlineStr">
@@ -18589,7 +18589,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK84" t="inlineStr">
@@ -18831,7 +18831,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -19240,7 +19240,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -19482,7 +19482,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK88" t="inlineStr">
@@ -19891,7 +19891,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK90" t="inlineStr">
@@ -20133,7 +20133,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -20542,7 +20542,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -20784,7 +20784,7 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK94" t="inlineStr">
@@ -21193,7 +21193,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK96" t="inlineStr">
@@ -21435,7 +21435,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
@@ -21844,7 +21844,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -22086,7 +22086,7 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK100" t="inlineStr">
@@ -22495,7 +22495,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK102" t="inlineStr">
@@ -22737,7 +22737,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -23146,7 +23146,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
@@ -23388,7 +23388,7 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK106" t="inlineStr">
@@ -23797,7 +23797,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK108" t="inlineStr">
@@ -24039,7 +24039,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
@@ -24448,7 +24448,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -24690,7 +24690,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK112" t="inlineStr">
@@ -25099,7 +25099,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK114" t="inlineStr">
@@ -25341,7 +25341,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
@@ -25750,7 +25750,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK117" t="inlineStr">
@@ -25992,7 +25992,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK118" t="inlineStr">
@@ -26401,7 +26401,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK120" t="inlineStr">
@@ -26643,7 +26643,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK121" t="inlineStr">
@@ -27052,7 +27052,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
@@ -27294,7 +27294,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK124" t="inlineStr">
@@ -27703,7 +27703,7 @@
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK126" t="inlineStr">
@@ -27945,7 +27945,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK127" t="inlineStr">
@@ -28354,7 +28354,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK129" t="inlineStr">
@@ -28596,7 +28596,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK130" t="inlineStr">
@@ -29005,7 +29005,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK132" t="inlineStr">
@@ -29247,7 +29247,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK133" t="inlineStr">
@@ -29656,7 +29656,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
@@ -29898,7 +29898,7 @@
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK136" t="inlineStr">
@@ -30307,7 +30307,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK138" t="inlineStr">
@@ -30549,7 +30549,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK139" t="inlineStr">
@@ -30958,7 +30958,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK141" t="inlineStr">
@@ -31200,7 +31200,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK142" t="inlineStr">
@@ -31609,7 +31609,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK144" t="inlineStr">
@@ -31851,7 +31851,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK145" t="inlineStr">
@@ -32260,7 +32260,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">
@@ -32502,7 +32502,7 @@
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK148" t="inlineStr">
@@ -32911,7 +32911,7 @@
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK150" t="inlineStr">
@@ -33153,7 +33153,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK151" t="inlineStr">
@@ -33562,7 +33562,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK153" t="inlineStr">
@@ -33804,7 +33804,7 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK154" t="inlineStr">
@@ -34213,7 +34213,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK156" t="inlineStr">
@@ -34455,7 +34455,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK157" t="inlineStr">
@@ -34864,7 +34864,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK159" t="inlineStr">
@@ -35106,7 +35106,7 @@
       </c>
       <c r="AJ160" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK160" t="inlineStr">
@@ -35515,7 +35515,7 @@
       </c>
       <c r="AJ162" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK162" t="inlineStr">
@@ -35757,7 +35757,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK163" t="inlineStr">
@@ -36166,7 +36166,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK165" t="inlineStr">
@@ -36408,7 +36408,7 @@
       </c>
       <c r="AJ166" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK166" t="inlineStr">
@@ -36817,7 +36817,7 @@
       </c>
       <c r="AJ168" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK168" t="inlineStr">
@@ -37059,7 +37059,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK169" t="inlineStr">
@@ -37468,7 +37468,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK171" t="inlineStr">
@@ -37710,7 +37710,7 @@
       </c>
       <c r="AJ172" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK172" t="inlineStr">
@@ -38119,7 +38119,7 @@
       </c>
       <c r="AJ174" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK174" t="inlineStr">
@@ -38361,7 +38361,7 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK175" t="inlineStr">
@@ -38770,7 +38770,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK177" t="inlineStr">
@@ -39012,7 +39012,7 @@
       </c>
       <c r="AJ178" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK178" t="inlineStr">
@@ -39421,7 +39421,7 @@
       </c>
       <c r="AJ180" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK180" t="inlineStr">
@@ -39663,7 +39663,7 @@
       </c>
       <c r="AJ181" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK181" t="inlineStr">
@@ -40072,7 +40072,7 @@
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK183" t="inlineStr">
@@ -40314,7 +40314,7 @@
       </c>
       <c r="AJ184" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK184" t="inlineStr">
@@ -40723,7 +40723,7 @@
       </c>
       <c r="AJ186" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK186" t="inlineStr">
@@ -40965,7 +40965,7 @@
       </c>
       <c r="AJ187" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK187" t="inlineStr">
@@ -41374,7 +41374,7 @@
       </c>
       <c r="AJ189" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK189" t="inlineStr">
@@ -41616,7 +41616,7 @@
       </c>
       <c r="AJ190" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK190" t="inlineStr">
@@ -42025,7 +42025,7 @@
       </c>
       <c r="AJ192" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK192" t="inlineStr">
@@ -42267,7 +42267,7 @@
       </c>
       <c r="AJ193" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK193" t="inlineStr">
@@ -42676,7 +42676,7 @@
       </c>
       <c r="AJ195" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK195" t="inlineStr">
@@ -42918,7 +42918,7 @@
       </c>
       <c r="AJ196" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK196" t="inlineStr">
@@ -43327,7 +43327,7 @@
       </c>
       <c r="AJ198" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK198" t="inlineStr">
@@ -43569,7 +43569,7 @@
       </c>
       <c r="AJ199" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK199" t="inlineStr">
@@ -43978,7 +43978,7 @@
       </c>
       <c r="AJ201" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK201" t="inlineStr">
@@ -44220,7 +44220,7 @@
       </c>
       <c r="AJ202" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK202" t="inlineStr">
@@ -44629,7 +44629,7 @@
       </c>
       <c r="AJ204" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK204" t="inlineStr">
@@ -44871,7 +44871,7 @@
       </c>
       <c r="AJ205" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK205" t="inlineStr">
@@ -45280,7 +45280,7 @@
       </c>
       <c r="AJ207" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK207" t="inlineStr">
@@ -45522,7 +45522,7 @@
       </c>
       <c r="AJ208" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK208" t="inlineStr">
@@ -45931,7 +45931,7 @@
       </c>
       <c r="AJ210" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK210" t="inlineStr">
@@ -46173,7 +46173,7 @@
       </c>
       <c r="AJ211" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK211" t="inlineStr">
@@ -46582,7 +46582,7 @@
       </c>
       <c r="AJ213" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK213" t="inlineStr">
@@ -46824,7 +46824,7 @@
       </c>
       <c r="AJ214" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK214" t="inlineStr">
@@ -47233,7 +47233,7 @@
       </c>
       <c r="AJ216" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK216" t="inlineStr">
@@ -47475,7 +47475,7 @@
       </c>
       <c r="AJ217" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK217" t="inlineStr">
@@ -47884,7 +47884,7 @@
       </c>
       <c r="AJ219" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK219" t="inlineStr">
@@ -48126,7 +48126,7 @@
       </c>
       <c r="AJ220" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK220" t="inlineStr">
@@ -48535,7 +48535,7 @@
       </c>
       <c r="AJ222" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK222" t="inlineStr">
@@ -48777,7 +48777,7 @@
       </c>
       <c r="AJ223" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK223" t="inlineStr">
@@ -49186,7 +49186,7 @@
       </c>
       <c r="AJ225" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK225" t="inlineStr">
@@ -49428,7 +49428,7 @@
       </c>
       <c r="AJ226" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK226" t="inlineStr">
@@ -49837,7 +49837,7 @@
       </c>
       <c r="AJ228" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK228" t="inlineStr">
@@ -50079,7 +50079,7 @@
       </c>
       <c r="AJ229" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK229" t="inlineStr">
@@ -50488,7 +50488,7 @@
       </c>
       <c r="AJ231" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK231" t="inlineStr">
@@ -50730,7 +50730,7 @@
       </c>
       <c r="AJ232" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK232" t="inlineStr">
@@ -51139,7 +51139,7 @@
       </c>
       <c r="AJ234" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK234" t="inlineStr">
@@ -51381,7 +51381,7 @@
       </c>
       <c r="AJ235" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK235" t="inlineStr">
@@ -51790,7 +51790,7 @@
       </c>
       <c r="AJ237" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK237" t="inlineStr">
@@ -52032,7 +52032,7 @@
       </c>
       <c r="AJ238" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK238" t="inlineStr">
@@ -52441,7 +52441,7 @@
       </c>
       <c r="AJ240" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK240" t="inlineStr">
@@ -52683,7 +52683,7 @@
       </c>
       <c r="AJ241" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK241" t="inlineStr">
@@ -53092,7 +53092,7 @@
       </c>
       <c r="AJ243" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK243" t="inlineStr">
@@ -53334,7 +53334,7 @@
       </c>
       <c r="AJ244" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK244" t="inlineStr">
@@ -53743,7 +53743,7 @@
       </c>
       <c r="AJ246" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK246" t="inlineStr">
@@ -53985,7 +53985,7 @@
       </c>
       <c r="AJ247" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK247" t="inlineStr">
@@ -54394,7 +54394,7 @@
       </c>
       <c r="AJ249" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK249" t="inlineStr">
@@ -54636,7 +54636,7 @@
       </c>
       <c r="AJ250" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK250" t="inlineStr">
@@ -55045,7 +55045,7 @@
       </c>
       <c r="AJ252" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK252" t="inlineStr">
@@ -55287,7 +55287,7 @@
       </c>
       <c r="AJ253" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK253" t="inlineStr">
@@ -55696,7 +55696,7 @@
       </c>
       <c r="AJ255" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK255" t="inlineStr">
@@ -55938,7 +55938,7 @@
       </c>
       <c r="AJ256" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK256" t="inlineStr">
@@ -56347,7 +56347,7 @@
       </c>
       <c r="AJ258" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK258" t="inlineStr">
@@ -56589,7 +56589,7 @@
       </c>
       <c r="AJ259" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK259" t="inlineStr">
@@ -56998,7 +56998,7 @@
       </c>
       <c r="AJ261" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK261" t="inlineStr">
@@ -57240,7 +57240,7 @@
       </c>
       <c r="AJ262" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK262" t="inlineStr">
@@ -57649,7 +57649,7 @@
       </c>
       <c r="AJ264" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK264" t="inlineStr">
@@ -57891,7 +57891,7 @@
       </c>
       <c r="AJ265" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK265" t="inlineStr">
@@ -58300,7 +58300,7 @@
       </c>
       <c r="AJ267" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK267" t="inlineStr">
@@ -58542,7 +58542,7 @@
       </c>
       <c r="AJ268" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK268" t="inlineStr">
@@ -58951,7 +58951,7 @@
       </c>
       <c r="AJ270" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK270" t="inlineStr">
@@ -59193,7 +59193,7 @@
       </c>
       <c r="AJ271" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK271" t="inlineStr">
@@ -59602,7 +59602,7 @@
       </c>
       <c r="AJ273" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK273" t="inlineStr">
@@ -59844,7 +59844,7 @@
       </c>
       <c r="AJ274" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK274" t="inlineStr">
@@ -60253,7 +60253,7 @@
       </c>
       <c r="AJ276" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK276" t="inlineStr">
@@ -60495,7 +60495,7 @@
       </c>
       <c r="AJ277" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK277" t="inlineStr">
@@ -60904,7 +60904,7 @@
       </c>
       <c r="AJ279" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK279" t="inlineStr">
@@ -61146,7 +61146,7 @@
       </c>
       <c r="AJ280" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK280" t="inlineStr">
@@ -61555,7 +61555,7 @@
       </c>
       <c r="AJ282" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK282" t="inlineStr">
@@ -61797,7 +61797,7 @@
       </c>
       <c r="AJ283" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK283" t="inlineStr">
@@ -62206,7 +62206,7 @@
       </c>
       <c r="AJ285" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK285" t="inlineStr">
@@ -62448,7 +62448,7 @@
       </c>
       <c r="AJ286" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK286" t="inlineStr">
@@ -62857,7 +62857,7 @@
       </c>
       <c r="AJ288" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK288" t="inlineStr">
@@ -63099,7 +63099,7 @@
       </c>
       <c r="AJ289" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK289" t="inlineStr">
@@ -63508,7 +63508,7 @@
       </c>
       <c r="AJ291" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK291" t="inlineStr">
@@ -63750,7 +63750,7 @@
       </c>
       <c r="AJ292" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK292" t="inlineStr">
@@ -64159,7 +64159,7 @@
       </c>
       <c r="AJ294" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK294" t="inlineStr">
@@ -64401,7 +64401,7 @@
       </c>
       <c r="AJ295" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK295" t="inlineStr">
@@ -64810,7 +64810,7 @@
       </c>
       <c r="AJ297" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK297" t="inlineStr">
@@ -65052,7 +65052,7 @@
       </c>
       <c r="AJ298" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK298" t="inlineStr">
@@ -65461,7 +65461,7 @@
       </c>
       <c r="AJ300" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK300" t="inlineStr">
@@ -65703,7 +65703,7 @@
       </c>
       <c r="AJ301" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK301" t="inlineStr">
@@ -66112,7 +66112,7 @@
       </c>
       <c r="AJ303" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK303" t="inlineStr">
@@ -66354,7 +66354,7 @@
       </c>
       <c r="AJ304" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK304" t="inlineStr">
@@ -66763,7 +66763,7 @@
       </c>
       <c r="AJ306" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK306" t="inlineStr">
@@ -67005,7 +67005,7 @@
       </c>
       <c r="AJ307" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK307" t="inlineStr">
@@ -67414,7 +67414,7 @@
       </c>
       <c r="AJ309" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK309" t="inlineStr">
@@ -67656,7 +67656,7 @@
       </c>
       <c r="AJ310" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK310" t="inlineStr">
@@ -68065,7 +68065,7 @@
       </c>
       <c r="AJ312" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK312" t="inlineStr">
@@ -68307,7 +68307,7 @@
       </c>
       <c r="AJ313" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK313" t="inlineStr">

--- a/diseases/d211/2020-2025.xlsx
+++ b/diseases/d211/2020-2025.xlsx
@@ -1012,7 +1012,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1254,7 +1254,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
@@ -1663,7 +1663,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
@@ -1905,7 +1905,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2314,7 +2314,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2556,7 +2556,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
@@ -2965,7 +2965,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
@@ -3207,7 +3207,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3616,7 +3616,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
@@ -4267,7 +4267,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
@@ -4509,7 +4509,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4918,7 +4918,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -5160,7 +5160,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
@@ -5569,7 +5569,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
@@ -5811,7 +5811,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -6220,7 +6220,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -6462,7 +6462,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
@@ -6871,7 +6871,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
@@ -7113,7 +7113,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -7522,7 +7522,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7764,7 +7764,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
@@ -8173,7 +8173,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
@@ -8415,7 +8415,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -8824,7 +8824,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -9066,7 +9066,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK40" t="inlineStr">
@@ -9475,7 +9475,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
@@ -9717,7 +9717,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -10126,7 +10126,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -10368,7 +10368,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
@@ -10777,7 +10777,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK48" t="inlineStr">
@@ -11019,7 +11019,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -11428,7 +11428,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -11670,7 +11670,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK52" t="inlineStr">
@@ -12079,7 +12079,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK54" t="inlineStr">
@@ -12321,7 +12321,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -12730,7 +12730,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -12972,7 +12972,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK58" t="inlineStr">
@@ -13381,7 +13381,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK60" t="inlineStr">
@@ -13623,7 +13623,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -14032,7 +14032,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -14274,7 +14274,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK64" t="inlineStr">
@@ -14683,7 +14683,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK66" t="inlineStr">
@@ -14925,7 +14925,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -15334,7 +15334,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -15576,7 +15576,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK70" t="inlineStr">
@@ -15985,7 +15985,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK72" t="inlineStr">
@@ -16227,7 +16227,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -16636,7 +16636,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -16878,7 +16878,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK76" t="inlineStr">
@@ -17287,7 +17287,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK78" t="inlineStr">
@@ -17529,7 +17529,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -17938,7 +17938,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -18180,7 +18180,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK82" t="inlineStr">
@@ -18589,7 +18589,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK84" t="inlineStr">
@@ -18831,7 +18831,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -19240,7 +19240,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -19482,7 +19482,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK88" t="inlineStr">
@@ -19891,7 +19891,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK90" t="inlineStr">
@@ -20133,7 +20133,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -20542,7 +20542,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -20784,7 +20784,7 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK94" t="inlineStr">
@@ -21193,7 +21193,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK96" t="inlineStr">
@@ -21435,7 +21435,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
@@ -21844,7 +21844,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -22086,7 +22086,7 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK100" t="inlineStr">
@@ -22495,7 +22495,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK102" t="inlineStr">
@@ -22737,7 +22737,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -23146,7 +23146,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
@@ -23388,7 +23388,7 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK106" t="inlineStr">
@@ -23797,7 +23797,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK108" t="inlineStr">
@@ -24039,7 +24039,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
@@ -24448,7 +24448,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -24690,7 +24690,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK112" t="inlineStr">
@@ -25099,7 +25099,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK114" t="inlineStr">
@@ -25341,7 +25341,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
@@ -25750,7 +25750,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK117" t="inlineStr">
@@ -25992,7 +25992,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK118" t="inlineStr">
@@ -26401,7 +26401,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK120" t="inlineStr">
@@ -26643,7 +26643,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK121" t="inlineStr">
@@ -27052,7 +27052,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
@@ -27294,7 +27294,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK124" t="inlineStr">
@@ -27703,7 +27703,7 @@
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK126" t="inlineStr">
@@ -27945,7 +27945,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK127" t="inlineStr">
@@ -28354,7 +28354,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK129" t="inlineStr">
@@ -28596,7 +28596,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK130" t="inlineStr">
@@ -29005,7 +29005,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK132" t="inlineStr">
@@ -29247,7 +29247,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK133" t="inlineStr">
@@ -29656,7 +29656,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
@@ -29898,7 +29898,7 @@
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK136" t="inlineStr">
@@ -30307,7 +30307,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK138" t="inlineStr">
@@ -30549,7 +30549,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK139" t="inlineStr">
@@ -30958,7 +30958,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK141" t="inlineStr">
@@ -31200,7 +31200,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK142" t="inlineStr">
@@ -31609,7 +31609,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK144" t="inlineStr">
@@ -31851,7 +31851,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK145" t="inlineStr">
@@ -32260,7 +32260,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">
@@ -32502,7 +32502,7 @@
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK148" t="inlineStr">
@@ -32911,7 +32911,7 @@
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK150" t="inlineStr">
@@ -33153,7 +33153,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK151" t="inlineStr">
@@ -33562,7 +33562,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK153" t="inlineStr">
@@ -33804,7 +33804,7 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK154" t="inlineStr">
@@ -34213,7 +34213,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK156" t="inlineStr">
@@ -34455,7 +34455,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK157" t="inlineStr">
@@ -34864,7 +34864,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK159" t="inlineStr">
@@ -35106,7 +35106,7 @@
       </c>
       <c r="AJ160" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK160" t="inlineStr">
@@ -35515,7 +35515,7 @@
       </c>
       <c r="AJ162" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK162" t="inlineStr">
@@ -35757,7 +35757,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK163" t="inlineStr">
@@ -36166,7 +36166,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK165" t="inlineStr">
@@ -36408,7 +36408,7 @@
       </c>
       <c r="AJ166" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK166" t="inlineStr">
@@ -36817,7 +36817,7 @@
       </c>
       <c r="AJ168" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK168" t="inlineStr">
@@ -37059,7 +37059,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK169" t="inlineStr">
@@ -37468,7 +37468,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK171" t="inlineStr">
@@ -37710,7 +37710,7 @@
       </c>
       <c r="AJ172" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK172" t="inlineStr">
@@ -38119,7 +38119,7 @@
       </c>
       <c r="AJ174" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK174" t="inlineStr">
@@ -38361,7 +38361,7 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK175" t="inlineStr">
@@ -38770,7 +38770,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK177" t="inlineStr">
@@ -39012,7 +39012,7 @@
       </c>
       <c r="AJ178" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK178" t="inlineStr">
@@ -39421,7 +39421,7 @@
       </c>
       <c r="AJ180" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK180" t="inlineStr">
@@ -39663,7 +39663,7 @@
       </c>
       <c r="AJ181" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK181" t="inlineStr">
@@ -40072,7 +40072,7 @@
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK183" t="inlineStr">
@@ -40314,7 +40314,7 @@
       </c>
       <c r="AJ184" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK184" t="inlineStr">
@@ -40723,7 +40723,7 @@
       </c>
       <c r="AJ186" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK186" t="inlineStr">
@@ -40965,7 +40965,7 @@
       </c>
       <c r="AJ187" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK187" t="inlineStr">
@@ -41374,7 +41374,7 @@
       </c>
       <c r="AJ189" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK189" t="inlineStr">
@@ -41616,7 +41616,7 @@
       </c>
       <c r="AJ190" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK190" t="inlineStr">
@@ -42025,7 +42025,7 @@
       </c>
       <c r="AJ192" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK192" t="inlineStr">
@@ -42267,7 +42267,7 @@
       </c>
       <c r="AJ193" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK193" t="inlineStr">
@@ -42676,7 +42676,7 @@
       </c>
       <c r="AJ195" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK195" t="inlineStr">
@@ -42918,7 +42918,7 @@
       </c>
       <c r="AJ196" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK196" t="inlineStr">
@@ -43327,7 +43327,7 @@
       </c>
       <c r="AJ198" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK198" t="inlineStr">
@@ -43569,7 +43569,7 @@
       </c>
       <c r="AJ199" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK199" t="inlineStr">
@@ -43978,7 +43978,7 @@
       </c>
       <c r="AJ201" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK201" t="inlineStr">
@@ -44220,7 +44220,7 @@
       </c>
       <c r="AJ202" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK202" t="inlineStr">
@@ -44629,7 +44629,7 @@
       </c>
       <c r="AJ204" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK204" t="inlineStr">
@@ -44871,7 +44871,7 @@
       </c>
       <c r="AJ205" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK205" t="inlineStr">
@@ -45280,7 +45280,7 @@
       </c>
       <c r="AJ207" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK207" t="inlineStr">
@@ -45522,7 +45522,7 @@
       </c>
       <c r="AJ208" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK208" t="inlineStr">
@@ -45931,7 +45931,7 @@
       </c>
       <c r="AJ210" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK210" t="inlineStr">
@@ -46173,7 +46173,7 @@
       </c>
       <c r="AJ211" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK211" t="inlineStr">
@@ -46582,7 +46582,7 @@
       </c>
       <c r="AJ213" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK213" t="inlineStr">
@@ -46824,7 +46824,7 @@
       </c>
       <c r="AJ214" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK214" t="inlineStr">
@@ -47233,7 +47233,7 @@
       </c>
       <c r="AJ216" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK216" t="inlineStr">
@@ -47475,7 +47475,7 @@
       </c>
       <c r="AJ217" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK217" t="inlineStr">
@@ -47884,7 +47884,7 @@
       </c>
       <c r="AJ219" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK219" t="inlineStr">
@@ -48126,7 +48126,7 @@
       </c>
       <c r="AJ220" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK220" t="inlineStr">
@@ -48535,7 +48535,7 @@
       </c>
       <c r="AJ222" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK222" t="inlineStr">
@@ -48777,7 +48777,7 @@
       </c>
       <c r="AJ223" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK223" t="inlineStr">
@@ -49186,7 +49186,7 @@
       </c>
       <c r="AJ225" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK225" t="inlineStr">
@@ -49428,7 +49428,7 @@
       </c>
       <c r="AJ226" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK226" t="inlineStr">
@@ -49837,7 +49837,7 @@
       </c>
       <c r="AJ228" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK228" t="inlineStr">
@@ -50079,7 +50079,7 @@
       </c>
       <c r="AJ229" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK229" t="inlineStr">
@@ -50488,7 +50488,7 @@
       </c>
       <c r="AJ231" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK231" t="inlineStr">
@@ -50730,7 +50730,7 @@
       </c>
       <c r="AJ232" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK232" t="inlineStr">
@@ -51139,7 +51139,7 @@
       </c>
       <c r="AJ234" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK234" t="inlineStr">
@@ -51381,7 +51381,7 @@
       </c>
       <c r="AJ235" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK235" t="inlineStr">
@@ -51790,7 +51790,7 @@
       </c>
       <c r="AJ237" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK237" t="inlineStr">
@@ -52032,7 +52032,7 @@
       </c>
       <c r="AJ238" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK238" t="inlineStr">
@@ -52441,7 +52441,7 @@
       </c>
       <c r="AJ240" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK240" t="inlineStr">
@@ -52683,7 +52683,7 @@
       </c>
       <c r="AJ241" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK241" t="inlineStr">
@@ -53092,7 +53092,7 @@
       </c>
       <c r="AJ243" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK243" t="inlineStr">
@@ -53334,7 +53334,7 @@
       </c>
       <c r="AJ244" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK244" t="inlineStr">
@@ -53743,7 +53743,7 @@
       </c>
       <c r="AJ246" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK246" t="inlineStr">
@@ -53985,7 +53985,7 @@
       </c>
       <c r="AJ247" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK247" t="inlineStr">
@@ -54394,7 +54394,7 @@
       </c>
       <c r="AJ249" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK249" t="inlineStr">
@@ -54636,7 +54636,7 @@
       </c>
       <c r="AJ250" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK250" t="inlineStr">
@@ -55045,7 +55045,7 @@
       </c>
       <c r="AJ252" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK252" t="inlineStr">
@@ -55287,7 +55287,7 @@
       </c>
       <c r="AJ253" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK253" t="inlineStr">
@@ -55696,7 +55696,7 @@
       </c>
       <c r="AJ255" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK255" t="inlineStr">
@@ -55938,7 +55938,7 @@
       </c>
       <c r="AJ256" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK256" t="inlineStr">
@@ -56347,7 +56347,7 @@
       </c>
       <c r="AJ258" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK258" t="inlineStr">
@@ -56589,7 +56589,7 @@
       </c>
       <c r="AJ259" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK259" t="inlineStr">
@@ -56998,7 +56998,7 @@
       </c>
       <c r="AJ261" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK261" t="inlineStr">
@@ -57240,7 +57240,7 @@
       </c>
       <c r="AJ262" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK262" t="inlineStr">
@@ -57649,7 +57649,7 @@
       </c>
       <c r="AJ264" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK264" t="inlineStr">
@@ -57891,7 +57891,7 @@
       </c>
       <c r="AJ265" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK265" t="inlineStr">
@@ -58300,7 +58300,7 @@
       </c>
       <c r="AJ267" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK267" t="inlineStr">
@@ -58542,7 +58542,7 @@
       </c>
       <c r="AJ268" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK268" t="inlineStr">
@@ -58951,7 +58951,7 @@
       </c>
       <c r="AJ270" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK270" t="inlineStr">
@@ -59193,7 +59193,7 @@
       </c>
       <c r="AJ271" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK271" t="inlineStr">
@@ -59602,7 +59602,7 @@
       </c>
       <c r="AJ273" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK273" t="inlineStr">
@@ -59844,7 +59844,7 @@
       </c>
       <c r="AJ274" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK274" t="inlineStr">
@@ -60253,7 +60253,7 @@
       </c>
       <c r="AJ276" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK276" t="inlineStr">
@@ -60495,7 +60495,7 @@
       </c>
       <c r="AJ277" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK277" t="inlineStr">
@@ -60904,7 +60904,7 @@
       </c>
       <c r="AJ279" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK279" t="inlineStr">
@@ -61146,7 +61146,7 @@
       </c>
       <c r="AJ280" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK280" t="inlineStr">
@@ -61555,7 +61555,7 @@
       </c>
       <c r="AJ282" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK282" t="inlineStr">
@@ -61797,7 +61797,7 @@
       </c>
       <c r="AJ283" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK283" t="inlineStr">
@@ -62206,7 +62206,7 @@
       </c>
       <c r="AJ285" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK285" t="inlineStr">
@@ -62448,7 +62448,7 @@
       </c>
       <c r="AJ286" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK286" t="inlineStr">
@@ -62857,7 +62857,7 @@
       </c>
       <c r="AJ288" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK288" t="inlineStr">
@@ -63099,7 +63099,7 @@
       </c>
       <c r="AJ289" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK289" t="inlineStr">
@@ -63508,7 +63508,7 @@
       </c>
       <c r="AJ291" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK291" t="inlineStr">
@@ -63750,7 +63750,7 @@
       </c>
       <c r="AJ292" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK292" t="inlineStr">
@@ -64159,7 +64159,7 @@
       </c>
       <c r="AJ294" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK294" t="inlineStr">
@@ -64401,7 +64401,7 @@
       </c>
       <c r="AJ295" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK295" t="inlineStr">
@@ -64810,7 +64810,7 @@
       </c>
       <c r="AJ297" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK297" t="inlineStr">
@@ -65052,7 +65052,7 @@
       </c>
       <c r="AJ298" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK298" t="inlineStr">
@@ -65461,7 +65461,7 @@
       </c>
       <c r="AJ300" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK300" t="inlineStr">
@@ -65703,7 +65703,7 @@
       </c>
       <c r="AJ301" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK301" t="inlineStr">
@@ -66112,7 +66112,7 @@
       </c>
       <c r="AJ303" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK303" t="inlineStr">
@@ -66354,7 +66354,7 @@
       </c>
       <c r="AJ304" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK304" t="inlineStr">
@@ -66763,7 +66763,7 @@
       </c>
       <c r="AJ306" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK306" t="inlineStr">
@@ -67005,7 +67005,7 @@
       </c>
       <c r="AJ307" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK307" t="inlineStr">
@@ -67414,7 +67414,7 @@
       </c>
       <c r="AJ309" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK309" t="inlineStr">
@@ -67656,7 +67656,7 @@
       </c>
       <c r="AJ310" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK310" t="inlineStr">
@@ -68065,7 +68065,7 @@
       </c>
       <c r="AJ312" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK312" t="inlineStr">
@@ -68307,7 +68307,7 @@
       </c>
       <c r="AJ313" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK313" t="inlineStr">
